--- a/documents/fixture-platny.xlsx
+++ b/documents/fixture-platny.xlsx
@@ -25,20 +25,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="277">
   <si>
     <t>Fixture — platný (testovací data, ne skutečná hra)</t>
   </si>
   <si>
+    <t>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</t>
+  </si>
+  <si>
+    <t>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</t>
+  </si>
+  <si>
     <t>Characters</t>
   </si>
   <si>
     <t>Groups</t>
   </si>
   <si>
-    <t>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</t>
-  </si>
-  <si>
     <t>Scales</t>
   </si>
   <si>
@@ -48,39 +51,42 @@
     <t>Character</t>
   </si>
   <si>
-    <t>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Min</t>
+  </si>
+  <si>
     <t>Funkcionari</t>
   </si>
   <si>
-    <t>Min</t>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Default</t>
   </si>
   <si>
     <t>Funkcionáři</t>
   </si>
   <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>SrdceParty</t>
   </si>
   <si>
+    <t>Marie</t>
+  </si>
+  <si>
     <t>Srdce party</t>
   </si>
   <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Marie</t>
-  </si>
-  <si>
     <t>S_Marie_Regime</t>
   </si>
   <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>Household</t>
+  </si>
+  <si>
     <t xml:space="preserve">S_Marie_Control </t>
   </si>
   <si>
@@ -90,18 +96,12 @@
     <t>S_Antonin_Activity</t>
   </si>
   <si>
-    <t>Surname</t>
-  </si>
-  <si>
     <t>Mirek</t>
   </si>
   <si>
     <t>S_Mirek_Regime</t>
   </si>
   <si>
-    <t>Household</t>
-  </si>
-  <si>
     <t>Balážová</t>
   </si>
   <si>
@@ -135,9 +135,159 @@
     <t>R_Mirek_Wealth</t>
   </si>
   <si>
+    <t>Questions</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>Scale and Resources Impact</t>
+  </si>
+  <si>
+    <t>Effects</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>ID Answer</t>
+  </si>
+  <si>
+    <t>Text response</t>
+  </si>
+  <si>
+    <t>Q_Marie_1_1</t>
+  </si>
+  <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>Kdo by měl vést partu ochránců přírody?</t>
+  </si>
+  <si>
+    <t>A_Marie_1_1_Antonin</t>
+  </si>
+  <si>
+    <t>R_Marie_Wealth+3, S_Marie_Regime-2</t>
+  </si>
+  <si>
+    <t>A_Marie_1_1_Mirek</t>
+  </si>
+  <si>
+    <t>R_Marie_Wealth+1</t>
+  </si>
+  <si>
+    <t>multi</t>
+  </si>
+  <si>
+    <t>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</t>
+  </si>
+  <si>
+    <t>A_Marie_1_2_Nikdo </t>
+  </si>
+  <si>
+    <t>Nikdo</t>
+  </si>
+  <si>
+    <t>A_Marie_1_2_Antonin</t>
+  </si>
+  <si>
+    <t>S_Marie_Regime+1</t>
+  </si>
+  <si>
+    <t>A_Marie_1_2_Mirek</t>
+  </si>
+  <si>
+    <t>R_Marie_Wealth+5; S_Marie_Control+1</t>
+  </si>
+  <si>
+    <t>A_Marie_1_2_Other</t>
+  </si>
+  <si>
+    <t>_OTHER_</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>Vybrali tě za novou členku skupiny Srdce party?</t>
+  </si>
+  <si>
+    <t>Ano</t>
+  </si>
+  <si>
+    <t>S_Marie_Regime-2</t>
+  </si>
+  <si>
+    <t>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_1_Prace</t>
+  </si>
+  <si>
+    <t>Práce</t>
+  </si>
+  <si>
+    <t>S_Antonin_Activity+1</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_1_Duchod</t>
+  </si>
+  <si>
+    <t>Důchod</t>
+  </si>
+  <si>
+    <t>S_Antonin_Activity-1</t>
+  </si>
+  <si>
+    <t>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_2_Deti</t>
+  </si>
+  <si>
+    <t>Děti</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_2_Klid</t>
+  </si>
+  <si>
+    <t>Klid</t>
+  </si>
+  <si>
+    <t>poll-answer</t>
+  </si>
+  <si>
+    <t>Q_Group_Funkcionari_Nastupce</t>
+  </si>
+  <si>
+    <t>Fotil jsi:</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_4_Funkcionare</t>
+  </si>
+  <si>
+    <t>Funkcionáře</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_4_Milovniky</t>
+  </si>
+  <si>
+    <t>Milovníky přírody</t>
+  </si>
+  <si>
+    <t>A_Antonin_1_4_Nikoho</t>
+  </si>
+  <si>
     <t>Block ID</t>
   </si>
   <si>
+    <t>Nikoho</t>
+  </si>
+  <si>
     <t>Variation ID</t>
   </si>
   <si>
@@ -153,72 +303,111 @@
     <t>Conditions</t>
   </si>
   <si>
+    <t>Došlo ke sňatku Marie a Mirka?</t>
+  </si>
+  <si>
     <t>B_Marie_1_Historie_1</t>
   </si>
   <si>
     <t>V_Marie_1_Historie_1_A</t>
   </si>
   <si>
+    <t>HOUSEHOLD_CREATE(Marie, Mirek)</t>
+  </si>
+  <si>
     <t>Antonín vede partu a Marie je radikální</t>
   </si>
   <si>
-    <t>Questions</t>
+    <t>scale_direct</t>
   </si>
   <si>
     <t>V uplynulém roce podpořila vedení party a její postoj k režimu se zostřil.</t>
   </si>
   <si>
+    <t>Nastav Mirkovu hodnotu Regime po poradě orgů.</t>
+  </si>
+  <si>
+    <t>A_Organizatori_1_2_Nastaveni</t>
+  </si>
+  <si>
+    <t>Nová hodnota</t>
+  </si>
+  <si>
     <t>A_Marie_1_1_Antonin AND S_Marie_Regime &gt;= 5</t>
   </si>
   <si>
+    <t>S_Mirek_Regime=VALUE</t>
+  </si>
+  <si>
     <t>V_Marie_1_Historie_1_B</t>
   </si>
   <si>
+    <t>resource_direct</t>
+  </si>
+  <si>
     <t>Antonín vede partu, nikdo jí nepomáhá</t>
   </si>
   <si>
+    <t>Nastav osobní účet Antonína po poradě orgů.</t>
+  </si>
+  <si>
     <t>Vedení party přijala s rezervou a o pomoc s Ekofilmem nikoho nepožádala.</t>
   </si>
   <si>
+    <t>A_Organizatori_1_3_Nastaveni</t>
+  </si>
+  <si>
     <t>A_Marie_1_1_Antonin AND !(A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
   </si>
   <si>
+    <t>R_Antonin_Wealth_private=VALUE</t>
+  </si>
+  <si>
     <t>V_Marie_1_Historie_1_C</t>
   </si>
   <si>
     <t>Náhoda 50 %</t>
   </si>
   <si>
+    <t>poll</t>
+  </si>
+  <si>
     <t>V uplynulém roce si pořídila kocoura.</t>
   </si>
   <si>
-    <t>Responses</t>
+    <t>Kdo by se podle tebe měl stát novým vedoucím směny?</t>
+  </si>
+  <si>
+    <t>A_Group_Funkcionari_Nastupce_Antonin</t>
   </si>
   <si>
     <t>!A_Marie_1_1_Antonin AND RANDOM(50)</t>
   </si>
   <si>
+    <t>Antonín Hájek</t>
+  </si>
+  <si>
     <t>V_Marie_1_Historie_1_D</t>
   </si>
   <si>
+    <t>A_Group_Funkcionari_Nastupce_Mirek</t>
+  </si>
+  <si>
     <t>Dobře se jí daří — text záměrně prázdný (nic se nestalo)</t>
   </si>
   <si>
+    <t>Mirek Pokorný</t>
+  </si>
+  <si>
     <t>R_Marie_Wealth &gt;= 7</t>
   </si>
   <si>
     <t>V_Marie_1_Historie_1_E</t>
   </si>
   <si>
-    <t>Scale and Resources Impact</t>
-  </si>
-  <si>
     <t>Fallback + zanořený blok</t>
   </si>
   <si>
-    <t>Effects</t>
-  </si>
-  <si>
     <t>Rok proběhl bez zásadních změn. {BLOK B_Marie_1_Historie_2}</t>
   </si>
   <si>
@@ -240,30 +429,18 @@
     <t>A_Marie_1_3_Ano</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>V_Marie_1_Historie_2_B</t>
   </si>
   <si>
     <t>Nepřijata (odpověď Ne bez řádku v listu)</t>
   </si>
   <si>
-    <t>Text</t>
-  </si>
-  <si>
     <t>Do Srdce party přijata nebyla.</t>
   </si>
   <si>
     <t>A_Marie_1_3_Ne</t>
   </si>
   <si>
-    <t>ID Answer</t>
-  </si>
-  <si>
-    <t>Text response</t>
-  </si>
-  <si>
     <t>V_Marie_1_Historie_2_C</t>
   </si>
   <si>
@@ -282,10 +459,7 @@
     <t>Doplňující otázka A pro další kapitolu.</t>
   </si>
   <si>
-    <t>Q_Marie_1_1</t>
-  </si>
-  <si>
-    <t>single</t>
+    <t>!A_Marie_1_1_Antonin</t>
   </si>
   <si>
     <t>V_Marie_1_Questions_1_B</t>
@@ -294,39 +468,21 @@
     <t>Fallback (prázdná podmínka)</t>
   </si>
   <si>
-    <t>Kdo by měl vést partu ochránců přírody?</t>
-  </si>
-  <si>
     <t>Doplňující otázka B pro další kapitolu.</t>
   </si>
   <si>
-    <t>A_Marie_1_1_Antonin</t>
-  </si>
-  <si>
     <t>B_Antonin_1_Historie_1</t>
   </si>
   <si>
     <t>V_Antonin_1_Historie_1_A</t>
   </si>
   <si>
-    <t>R_Marie_Wealth+3, S_Marie_Regime-2</t>
-  </si>
-  <si>
     <t>Je plně v důchodu</t>
   </si>
   <si>
     <t>Je plně v důchodu.</t>
   </si>
   <si>
-    <t>A_Marie_1_1_Mirek</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_1_Duchod</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth+1</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Historie_1_B</t>
   </si>
   <si>
@@ -336,75 +492,42 @@
     <t>Pracuje jako vrátný při důchodu.</t>
   </si>
   <si>
-    <t>multi</t>
-  </si>
-  <si>
     <t>B_Antonin_1_Historie_2</t>
   </si>
   <si>
-    <t>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Historie_2_A</t>
   </si>
   <si>
-    <t>A_Marie_1_2_Nikdo </t>
-  </si>
-  <si>
     <t>Vedoucím směny se stal Mirek</t>
   </si>
   <si>
-    <t>Nikdo</t>
-  </si>
-  <si>
     <t>Vedoucím směny se stal mladší kolega.</t>
   </si>
   <si>
-    <t>A_Group_Funkcionari_Nastupce_Mirek</t>
-  </si>
-  <si>
-    <t>A_Marie_1_2_Antonin</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Historie_2_B</t>
   </si>
   <si>
-    <t>S_Marie_Regime+1</t>
-  </si>
-  <si>
     <t>Zůstává on</t>
   </si>
   <si>
     <t>Vedoucím směny zůstal on sám.</t>
   </si>
   <si>
-    <t>A_Marie_1_2_Mirek</t>
-  </si>
-  <si>
     <t>B_Antonin_1_Historie_3</t>
   </si>
   <si>
     <t>V_Antonin_1_Historie_3_C</t>
   </si>
   <si>
-    <t>R_Marie_Wealth+5; S_Marie_Control+1</t>
-  </si>
-  <si>
     <t>Fallback stojí na řádku první, ale má nejvyšší číslo</t>
   </si>
   <si>
     <t>Rok byl klidný.</t>
   </si>
   <si>
-    <t>A_Marie_1_2_Other</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Historie_3_A</t>
   </si>
   <si>
-    <t>_OTHER_</t>
-  </si>
-  <si>
     <t>Aktivní + hlídá děti</t>
   </si>
   <si>
@@ -414,27 +537,15 @@
     <t>A_Antonin_1_2_Deti AND S_Antonin_Activity &gt;= 5</t>
   </si>
   <si>
-    <t>bool</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Historie_3_B</t>
   </si>
   <si>
-    <t>Vybrali tě za novou členku skupiny Srdce party?</t>
-  </si>
-  <si>
     <t>Aktivní</t>
   </si>
   <si>
     <t>Rok byl plný práce.</t>
   </si>
   <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime-2</t>
-  </si>
-  <si>
     <t>S_Antonin_Activity &gt;= 5</t>
   </si>
   <si>
@@ -450,27 +561,12 @@
     <t>Fotil funkcionáře.</t>
   </si>
   <si>
-    <t>A_Antonin_1_4_Funkcionare</t>
-  </si>
-  <si>
-    <t>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_1_Prace</t>
-  </si>
-  <si>
     <t>V_Antonin_1_Foto_1_B</t>
   </si>
   <si>
-    <t>Práce</t>
-  </si>
-  <si>
     <t>Fotil něco jiného.</t>
   </si>
   <si>
-    <t>S_Antonin_Activity+1</t>
-  </si>
-  <si>
     <t>B_Mirek_1_Historie_1</t>
   </si>
   <si>
@@ -480,13 +576,7 @@
     <t>Vyhrál anketu</t>
   </si>
   <si>
-    <t>Důchod</t>
-  </si>
-  <si>
     <t>Stal se vedoucím směny.</t>
-  </si>
-  <si>
-    <t>S_Antonin_Activity-1</t>
   </si>
   <si>
     <t xml:space="preserve">A_Group_Funkcionari_Nastupce_Mirek
@@ -502,15 +592,6 @@
     <t>Vedoucím směny se nestal.</t>
   </si>
   <si>
-    <t>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_2_Deti</t>
-  </si>
-  <si>
-    <t>Děti</t>
-  </si>
-  <si>
     <t>B_Funkcionari_1_Vedeni_1</t>
   </si>
   <si>
@@ -523,27 +604,15 @@
     <t>Vedení převzal mladší člen.</t>
   </si>
   <si>
-    <t>A_Antonin_1_2_Klid</t>
-  </si>
-  <si>
-    <t>Klid</t>
-  </si>
-  <si>
     <t>V_Funkcionari_1_Vedeni_1_B</t>
   </si>
   <si>
     <t>Vedení zůstalo beze změny.</t>
   </si>
   <si>
-    <t>poll-answer</t>
-  </si>
-  <si>
     <t>B_SrdceParty_1_Clenove_1</t>
   </si>
   <si>
-    <t>Q_Group_Funkcionari_Nastupce</t>
-  </si>
-  <si>
     <t>V_SrdceParty_1_Clenove_1_A</t>
   </si>
   <si>
@@ -553,286 +622,220 @@
     <t>Skupina přijala nového člena.</t>
   </si>
   <si>
-    <t>Fotil jsi:</t>
-  </si>
-  <si>
     <t>V_SrdceParty_1_Clenove_1_B</t>
   </si>
   <si>
     <t>Složení skupiny se nezměnilo.</t>
   </si>
   <si>
-    <t>Funkcionáře</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_4_Milovniky</t>
-  </si>
-  <si>
-    <t>Milovníky přírody</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_4_Nikoho</t>
-  </si>
-  <si>
-    <t>Nikoho</t>
-  </si>
-  <si>
-    <t>Došlo ke sňatku Marie a Mirka?</t>
-  </si>
-  <si>
-    <t>HOUSEHOLD_CREATE(Marie, Mirek)</t>
-  </si>
-  <si>
-    <t>scale_direct</t>
-  </si>
-  <si>
-    <t>Nastav Mirkovu hodnotu Regime po poradě orgů.</t>
-  </si>
-  <si>
-    <t>A_Organizatori_1_2_Nastaveni</t>
-  </si>
-  <si>
-    <t>Nová hodnota</t>
-  </si>
-  <si>
-    <t>S_Mirek_Regime=VALUE</t>
-  </si>
-  <si>
-    <t>resource_direct</t>
-  </si>
-  <si>
-    <t>Nastav osobní účet Antonína po poradě orgů.</t>
-  </si>
-  <si>
-    <t>A_Organizatori_1_3_Nastaveni</t>
-  </si>
-  <si>
-    <t>R_Antonin_Wealth_private=VALUE</t>
-  </si>
-  <si>
-    <t>poll</t>
-  </si>
-  <si>
-    <t>Kdo by se podle tebe měl stát novým vedoucím směny?</t>
-  </si>
-  <si>
-    <t>A_Group_Funkcionari_Nastupce_Antonin</t>
-  </si>
-  <si>
-    <t>Antonín Hájek</t>
-  </si>
-  <si>
-    <t>Mirek Pokorný</t>
-  </si>
-  <si>
     <t>Condition</t>
   </si>
   <si>
+    <t>B_Marie_2_Historie_1</t>
+  </si>
+  <si>
+    <t>V_Marie_2_Historie_1_A</t>
+  </si>
+  <si>
+    <t>Vystoupila veřejně</t>
+  </si>
+  <si>
+    <t>Veřejně vystoupila proti režimu.</t>
+  </si>
+  <si>
+    <t>A_Marie_2_2_Ano</t>
+  </si>
+  <si>
     <t>Podaří se Marii zorganizovat lokální verzi Ekofilmu? Kdo přislíbil pomoc?</t>
   </si>
   <si>
     <t>A_Marie_2_1_Nikdo</t>
   </si>
   <si>
+    <t>V_Marie_2_Historie_1_B</t>
+  </si>
+  <si>
+    <t>Přispěla na fond</t>
+  </si>
+  <si>
+    <t>Přispěla na stávkový fond a zbylo jí dost peněz.</t>
+  </si>
+  <si>
     <t>A_Marie_2_1_Antonin</t>
   </si>
   <si>
+    <t>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</t>
+  </si>
+  <si>
     <t>S_Marie_Control+1</t>
   </si>
   <si>
+    <t>V_Marie_2_Historie_1_C</t>
+  </si>
+  <si>
     <t>A_Marie_2_1_Mirek</t>
   </si>
   <si>
+    <t>Držela se v ústraní.</t>
+  </si>
+  <si>
     <t>R_Marie_Wealth+2</t>
   </si>
   <si>
     <t>A_Marie_2_1_Other</t>
   </si>
   <si>
+    <t>B_Antonin_2_Auto_1</t>
+  </si>
+  <si>
+    <t>V_Antonin_2_Auto_1_A</t>
+  </si>
+  <si>
     <t>S_Marie_Regime &gt;= 5 AND (A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
   </si>
   <si>
+    <t>Auto dostal Mirek</t>
+  </si>
+  <si>
+    <t>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</t>
+  </si>
+  <si>
     <t>Vystoupíš veřejně proti režimu?</t>
   </si>
   <si>
+    <t>A_Antonin_2_1_Mirek</t>
+  </si>
+  <si>
     <t>S_Marie_Regime+2, S_Marie_Control-1</t>
   </si>
   <si>
+    <t>V_Antonin_2_Auto_1_B</t>
+  </si>
+  <si>
     <t>Ne</t>
   </si>
   <si>
+    <t>Auto si nechal.</t>
+  </si>
+  <si>
     <t>Přispěješ na stávkový fond?</t>
   </si>
   <si>
+    <t>B_Antonin_2_Auto_2</t>
+  </si>
+  <si>
+    <t>V_Antonin_2_Auto_2_A</t>
+  </si>
+  <si>
     <t>R_Marie_Wealth_private-3</t>
   </si>
   <si>
+    <t>Poslední projížďka</t>
+  </si>
+  <si>
+    <t>Před předáním se s ním naposled projel.</t>
+  </si>
+  <si>
+    <t>A_Antonin_2_2_Ano</t>
+  </si>
+  <si>
     <t>Komu daruješ automobil s garáží?</t>
   </si>
   <si>
-    <t>A_Antonin_2_1_Mirek</t>
+    <t>V_Antonin_2_Auto_2_B</t>
   </si>
   <si>
     <t>R_Antonin_Wealth-10, R_Mirek_Wealth+10</t>
   </si>
   <si>
+    <t>Fallback — nic se nestalo</t>
+  </si>
+  <si>
     <t>A_Antonin_2_1_Nikdo</t>
   </si>
   <si>
     <t>Nikomu</t>
   </si>
   <si>
+    <t>B_Antonin_2_Stavka_1</t>
+  </si>
+  <si>
+    <t>V_Antonin_2_Stavka_1_A</t>
+  </si>
+  <si>
+    <t>Podpořil stávku</t>
+  </si>
+  <si>
+    <t>Stávku veřejně podpořil.</t>
+  </si>
+  <si>
     <t>Podpoříš veřejně ekologickou stávku v podniku?</t>
   </si>
   <si>
-    <t>A_Antonin_2_2_Ano</t>
+    <t>V_Antonin_2_Stavka_1_B</t>
+  </si>
+  <si>
+    <t>Nepodpořil</t>
+  </si>
+  <si>
+    <t>Ke stávce se nepřidal.</t>
   </si>
   <si>
     <t>A_Antonin_2_2_Ne</t>
   </si>
   <si>
+    <t>V_Antonin_2_Stavka_1_C</t>
+  </si>
+  <si>
+    <t>Fallback — otázka se nekladla</t>
+  </si>
+  <si>
+    <t>Stávka se ho netýkala.</t>
+  </si>
+  <si>
+    <t>B_Funkcionari_2_Vedeni_1</t>
+  </si>
+  <si>
+    <t>V_Funkcionari_2_Vedeni_1_A</t>
+  </si>
+  <si>
+    <t>Aktivní vedení</t>
+  </si>
+  <si>
+    <t>Vedení bylo aktivní.</t>
+  </si>
+  <si>
+    <t>V_Funkcionari_2_Vedeni_1_B</t>
+  </si>
+  <si>
     <t>Kdo má nést odpovědnost za nesrovnalosti ve skladu materiálu?</t>
   </si>
   <si>
     <t>A_Antonin_2_3_Mirek</t>
   </si>
   <si>
+    <t>Vedení bylo pasivní.</t>
+  </si>
+  <si>
     <t>A_Antonin_2_3_Nikdo</t>
   </si>
   <si>
+    <t>B_Funkcionari_2_Zapis_1</t>
+  </si>
+  <si>
+    <t>V_Funkcionari_2_Zapis_1_A</t>
+  </si>
+  <si>
+    <t>Jediná varianta = fallback</t>
+  </si>
+  <si>
+    <t>Zápis ze schůze byl archivován.</t>
+  </si>
+  <si>
     <t>Došlo k rozvodu Marie a Mirka?</t>
   </si>
   <si>
     <t>HOUSEHOLD_DELETE(Marie, Mirek)</t>
-  </si>
-  <si>
-    <t>B_Marie_2_Historie_1</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_A</t>
-  </si>
-  <si>
-    <t>Vystoupila veřejně</t>
-  </si>
-  <si>
-    <t>Veřejně vystoupila proti režimu.</t>
-  </si>
-  <si>
-    <t>A_Marie_2_2_Ano</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_B</t>
-  </si>
-  <si>
-    <t>Přispěla na fond</t>
-  </si>
-  <si>
-    <t>Přispěla na stávkový fond a zbylo jí dost peněz.</t>
-  </si>
-  <si>
-    <t>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_C</t>
-  </si>
-  <si>
-    <t>Držela se v ústraní.</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Auto_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_1_A</t>
-  </si>
-  <si>
-    <t>Auto dostal Mirek</t>
-  </si>
-  <si>
-    <t>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_1_B</t>
-  </si>
-  <si>
-    <t>Auto si nechal.</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Auto_2</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_2_A</t>
-  </si>
-  <si>
-    <t>Poslední projížďka</t>
-  </si>
-  <si>
-    <t>Před předáním se s ním naposled projel.</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_2_B</t>
-  </si>
-  <si>
-    <t>Fallback — nic se nestalo</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Stavka_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_A</t>
-  </si>
-  <si>
-    <t>Podpořil stávku</t>
-  </si>
-  <si>
-    <t>Stávku veřejně podpořil.</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_B</t>
-  </si>
-  <si>
-    <t>Nepodpořil</t>
-  </si>
-  <si>
-    <t>Ke stávce se nepřidal.</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_C</t>
-  </si>
-  <si>
-    <t>Fallback — otázka se nekladla</t>
-  </si>
-  <si>
-    <t>Stávka se ho netýkala.</t>
-  </si>
-  <si>
-    <t>B_Funkcionari_2_Vedeni_1</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Vedeni_1_A</t>
-  </si>
-  <si>
-    <t>Aktivní vedení</t>
-  </si>
-  <si>
-    <t>Vedení bylo aktivní.</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Vedeni_1_B</t>
-  </si>
-  <si>
-    <t>Vedení bylo pasivní.</t>
-  </si>
-  <si>
-    <t>B_Funkcionari_2_Zapis_1</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Zapis_1_A</t>
-  </si>
-  <si>
-    <t>Jediná varianta = fallback</t>
-  </si>
-  <si>
-    <t>Zápis ze schůze byl archivován.</t>
   </si>
   <si>
     <t>Vstoupila jsi do nové strany?</t>
@@ -873,12 +876,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font/>
     <font>
       <b/>
       <color theme="1"/>
@@ -943,35 +946,38 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1232,13 +1238,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>3</v>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
+      <c r="A3" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2249,103 +2255,103 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>63</v>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4">
-      <c r="G4" s="11" t="s">
-        <v>210</v>
+      <c r="G4" s="10" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>136</v>
+        <v>21</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>173</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>271</v>
+        <v>45</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>272</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="G5" s="11" t="s">
         <v>273</v>
       </c>
+      <c r="G5" s="10" t="s">
+        <v>274</v>
+      </c>
       <c r="H5" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="F6" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="G6" s="11" t="s">
         <v>275</v>
       </c>
+      <c r="G6" s="10" t="s">
+        <v>276</v>
+      </c>
       <c r="H6" s="8" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3354,33 +3360,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="4"/>
+      <c r="A1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>25</v>
@@ -3388,7 +3394,7 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>26</v>
@@ -3399,7 +3405,7 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>28</v>
@@ -4420,14 +4426,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="4"/>
+      <c r="A1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>8</v>
@@ -4435,18 +4441,18 @@
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5455,34 +5461,34 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4"/>
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>17</v>
@@ -5499,7 +5505,7 @@
     </row>
     <row r="4">
       <c r="B4" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" s="8">
         <v>1.0</v>
@@ -5513,10 +5519,10 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8">
         <v>1.0</v>
@@ -5530,10 +5536,10 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="8">
         <v>1.0</v>
@@ -6550,26 +6556,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="4"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>33</v>
@@ -6580,7 +6586,7 @@
     </row>
     <row r="4">
       <c r="A4" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>34</v>
@@ -6591,7 +6597,7 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>35</v>
@@ -7610,135 +7616,135 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F1" s="4"/>
-      <c r="G1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>63</v>
+      <c r="A1" s="3"/>
+      <c r="B1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="C2" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>89</v>
+        <v>45</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
       <c r="E4" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>22</v>
+        <v>49</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>105</v>
+        <v>51</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>109</v>
+        <v>53</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="E6" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="E7" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>22</v>
+        <v>57</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8">
       <c r="E8" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>125</v>
+        <v>59</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>135</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -7746,116 +7752,116 @@
         <v>26</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>142</v>
+        <v>45</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>145</v>
+        <v>66</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="E11" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>151</v>
+        <v>69</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>70</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>158</v>
+        <v>45</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>160</v>
+        <v>73</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="E13" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>166</v>
+        <v>75</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>171</v>
+        <v>77</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>175</v>
+        <v>45</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>79</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>178</v>
+        <v>80</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>81</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16">
       <c r="E16" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>180</v>
+        <v>82</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>182</v>
+        <v>84</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>86</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>171</v>
+        <v>77</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -7863,77 +7869,77 @@
         <v>30</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="12" t="s">
-        <v>184</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>186</v>
+        <v>97</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>99</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>188</v>
+        <v>100</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="C21" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>191</v>
+        <v>105</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>188</v>
+        <v>109</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>101</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1">
       <c r="B23" s="8" t="s">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>195</v>
+        <v>114</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>197</v>
+        <v>117</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="E24" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>198</v>
+        <v>121</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -8942,159 +8948,159 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>41</v>
+      <c r="A1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>46</v>
+        <v>94</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>98</v>
       </c>
       <c r="F2" s="8">
         <v>1.0</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>47</v>
+      <c r="G2" s="10" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>50</v>
+        <v>104</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>108</v>
       </c>
       <c r="F3" s="8">
         <v>2.0</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>51</v>
+      <c r="G3" s="10" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>54</v>
+        <v>112</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="F4" s="8">
         <v>3.0</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>56</v>
+      <c r="G4" s="10" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>58</v>
+        <v>120</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>122</v>
       </c>
       <c r="F5" s="8">
         <v>4.0</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>59</v>
+      <c r="G5" s="10" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>64</v>
+        <v>125</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="F6" s="8">
         <v>5.0</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>65</v>
+      <c r="G6" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>69</v>
+        <v>130</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>132</v>
       </c>
       <c r="F7" s="8">
         <v>1.0</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>70</v>
+      <c r="G7" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>75</v>
+        <v>134</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="F8" s="8">
         <v>2.0</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>76</v>
+      <c r="G8" s="10" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>80</v>
+        <v>138</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="F9" s="8">
         <v>3.0</v>
@@ -9102,192 +9108,192 @@
     </row>
     <row r="10">
       <c r="B10" s="8" t="s">
-        <v>81</v>
+        <v>140</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>56</v>
+        <v>141</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>90</v>
+        <v>145</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>96</v>
+        <v>149</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="F12" s="8">
         <v>1.0</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>98</v>
+      <c r="G12" s="10" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>102</v>
+        <v>152</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="F13" s="8">
         <v>2.0</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>65</v>
+      <c r="G13" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>110</v>
+        <v>156</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>158</v>
       </c>
       <c r="F14" s="8">
         <v>1.0</v>
       </c>
-      <c r="G14" s="11" t="s">
-        <v>111</v>
+      <c r="G14" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>116</v>
+        <v>159</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>161</v>
       </c>
       <c r="F15" s="8">
         <v>2.0</v>
       </c>
-      <c r="G15" s="11" t="s">
-        <v>65</v>
+      <c r="G15" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="s">
-        <v>118</v>
+        <v>162</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>122</v>
+        <v>163</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>165</v>
       </c>
       <c r="F16" s="8">
         <v>3.0</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>65</v>
+      <c r="G16" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>127</v>
+        <v>166</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="F17" s="8">
         <v>1.0</v>
       </c>
-      <c r="G17" s="11" t="s">
-        <v>128</v>
+      <c r="G17" s="10" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>133</v>
+        <v>170</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>172</v>
       </c>
       <c r="F18" s="8">
         <v>2.0</v>
       </c>
-      <c r="G18" s="11" t="s">
-        <v>136</v>
+      <c r="G18" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="8" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>140</v>
+        <v>175</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>177</v>
       </c>
       <c r="F19" s="8">
         <v>1.0</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>141</v>
+      <c r="G19" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>146</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>179</v>
       </c>
       <c r="F20" s="8">
         <v>2.0</v>
@@ -9295,122 +9301,122 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>152</v>
+        <v>181</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="F21" s="8">
         <v>1.0</v>
       </c>
-      <c r="G21" s="11" t="s">
-        <v>154</v>
+      <c r="G21" s="10" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="C22" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>157</v>
+        <v>185</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>187</v>
       </c>
       <c r="F22" s="8">
         <v>2.0</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>65</v>
+      <c r="G22" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>164</v>
+        <v>189</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>191</v>
       </c>
       <c r="F23" s="8">
         <v>1.0</v>
       </c>
-      <c r="G23" s="11" t="s">
-        <v>111</v>
+      <c r="G23" s="10" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="C24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>168</v>
+        <v>192</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>193</v>
       </c>
       <c r="F24" s="8">
         <v>2.0</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>65</v>
+      <c r="G24" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>174</v>
+        <v>195</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="F25" s="8">
         <v>1.0</v>
       </c>
-      <c r="G25" s="11" t="s">
-        <v>70</v>
+      <c r="G25" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="C26" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>177</v>
+        <v>198</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="F26" s="8">
         <v>2.0</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>65</v>
+      <c r="G26" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -10415,220 +10421,220 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="4"/>
-      <c r="H1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>63</v>
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="6"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="5"/>
+      <c r="H1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>5</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>56</v>
+        <v>15</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>118</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>200</v>
+        <v>51</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>206</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>109</v>
+        <v>207</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="4">
       <c r="F4" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="G4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
       <c r="F5" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>22</v>
+        <v>215</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
       <c r="F6" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>125</v>
+        <v>218</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="11" t="s">
-        <v>207</v>
+      <c r="B7" s="10" t="s">
+        <v>221</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="11" t="s">
-        <v>210</v>
+      <c r="G8" s="10" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="11" t="s">
-        <v>59</v>
+      <c r="B9" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>213</v>
+        <v>45</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>237</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>22</v>
+        <v>225</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
       <c r="F11" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>217</v>
+        <v>241</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="11" t="s">
-        <v>143</v>
+      <c r="B12" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>218</v>
+        <v>61</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>134</v>
+        <v>236</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>147</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
       <c r="F13" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>210</v>
+        <v>251</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>228</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>153</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="s">
-        <v>65</v>
+      <c r="B14" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>221</v>
+        <v>45</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>260</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>22</v>
+        <v>261</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>109</v>
+        <v>263</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -10636,17 +10642,17 @@
         <v>30</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="H16" s="8"/>
       <c r="I16" s="12" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -11659,265 +11665,265 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>41</v>
+      <c r="A1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>229</v>
+        <v>202</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>204</v>
       </c>
       <c r="F2" s="8">
         <v>1.0</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>230</v>
+      <c r="G2" s="10" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>233</v>
+        <v>208</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>210</v>
       </c>
       <c r="F3" s="8">
         <v>2.0</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>234</v>
+      <c r="G3" s="10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="4">
       <c r="C4" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>236</v>
+        <v>214</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>216</v>
       </c>
       <c r="F4" s="8">
         <v>3.0</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>65</v>
+      <c r="G4" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>240</v>
+        <v>220</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="F5" s="8">
         <v>1.0</v>
       </c>
-      <c r="G5" s="11" t="s">
-        <v>214</v>
+      <c r="G5" s="10" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>242</v>
+        <v>227</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>229</v>
       </c>
       <c r="F6" s="8">
         <v>2.0</v>
       </c>
-      <c r="G6" s="11" t="s">
-        <v>65</v>
+      <c r="G6" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>246</v>
+        <v>232</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="F7" s="8">
         <v>1.0</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>219</v>
+      <c r="G7" s="10" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>248</v>
+        <v>238</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>240</v>
       </c>
       <c r="F8" s="8">
         <v>2.0</v>
       </c>
-      <c r="G8" s="11" t="s">
-        <v>65</v>
+      <c r="G8" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>252</v>
+        <v>244</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="F9" s="8">
         <v>1.0</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>219</v>
+      <c r="G9" s="10" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>255</v>
+        <v>248</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="F10" s="8">
         <v>2.0</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>220</v>
+      <c r="G10" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>258</v>
+        <v>252</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>254</v>
       </c>
       <c r="F11" s="8">
         <v>3.0</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>65</v>
+      <c r="G11" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>262</v>
+        <v>256</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>258</v>
       </c>
       <c r="F12" s="8">
         <v>1.0</v>
       </c>
-      <c r="G12" s="11" t="s">
-        <v>136</v>
+      <c r="G12" s="10" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>264</v>
+        <v>259</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>262</v>
       </c>
       <c r="F13" s="8">
         <v>2.0</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>65</v>
+      <c r="G13" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/documents/fixture-platny.xlsx
+++ b/documents/fixture-platny.xlsx
@@ -1,1030 +1,87 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet state="visible" name="NOTES" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Characters" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Groups" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="Scales" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="Resources" sheetId="5" r:id="rId8"/>
-    <sheet state="visible" name="1_Questions" sheetId="6" r:id="rId9"/>
-    <sheet state="visible" name="2_Content" sheetId="7" r:id="rId10"/>
-    <sheet state="visible" name="2_Questions" sheetId="8" r:id="rId11"/>
-    <sheet state="visible" name="3_Content" sheetId="9" r:id="rId12"/>
-    <sheet state="visible" name="3_Questions" sheetId="10" r:id="rId13"/>
+    <sheet name="NOTES" sheetId="1" r:id="rId1"/>
+    <sheet name="Characters" sheetId="2" r:id="rId2"/>
+    <sheet name="Groups" sheetId="3" r:id="rId3"/>
+    <sheet name="Scales" sheetId="4" r:id="rId4"/>
+    <sheet name="Resources" sheetId="5" r:id="rId5"/>
+    <sheet name="1_Questions" sheetId="6" r:id="rId6"/>
+    <sheet name="2_Content" sheetId="7" r:id="rId7"/>
+    <sheet name="2_Questions" sheetId="8" r:id="rId8"/>
+    <sheet name="3_Content" sheetId="9" r:id="rId9"/>
+    <sheet name="3_Questions" sheetId="10" r:id="rId10"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId14" roundtripDataChecksum="kKtZz7r8t+I8PscWzbcxieEa+Z0ZsyIydMCto19Idq4="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="277">
-  <si>
-    <t>Fixture — platný (testovací data, ne skutečná hra)</t>
-  </si>
-  <si>
-    <t>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</t>
-  </si>
-  <si>
-    <t>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</t>
-  </si>
-  <si>
-    <t>Characters</t>
-  </si>
-  <si>
-    <t>Groups</t>
-  </si>
-  <si>
-    <t>Scales</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Character</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Funkcionari</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Funkcionáři</t>
-  </si>
-  <si>
-    <t>SrdceParty</t>
-  </si>
-  <si>
-    <t>Marie</t>
-  </si>
-  <si>
-    <t>Srdce party</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime</t>
-  </si>
-  <si>
-    <t>Surname</t>
-  </si>
-  <si>
-    <t>Household</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S_Marie_Control </t>
-  </si>
-  <si>
-    <t>Antonin</t>
-  </si>
-  <si>
-    <t>S_Antonin_Activity</t>
-  </si>
-  <si>
-    <t>Mirek</t>
-  </si>
-  <si>
-    <t>S_Mirek_Regime</t>
-  </si>
-  <si>
-    <t>Balážová</t>
-  </si>
-  <si>
-    <t>Antonín</t>
-  </si>
-  <si>
-    <t>Hájek</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Mirek</t>
-  </si>
-  <si>
-    <t>Pokorný</t>
-  </si>
-  <si>
-    <t>Organizatori</t>
-  </si>
-  <si>
-    <t>Organizátoři</t>
-  </si>
-  <si>
-    <t>Resources</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth</t>
-  </si>
-  <si>
-    <t>R_Antonin_Wealth</t>
-  </si>
-  <si>
-    <t>R_Mirek_Wealth</t>
-  </si>
-  <si>
-    <t>Questions</t>
-  </si>
-  <si>
-    <t>Responses</t>
-  </si>
-  <si>
-    <t>Scale and Resources Impact</t>
-  </si>
-  <si>
-    <t>Effects</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Text</t>
-  </si>
-  <si>
-    <t>ID Answer</t>
-  </si>
-  <si>
-    <t>Text response</t>
-  </si>
-  <si>
-    <t>Q_Marie_1_1</t>
-  </si>
-  <si>
-    <t>single</t>
-  </si>
-  <si>
-    <t>Kdo by měl vést partu ochránců přírody?</t>
-  </si>
-  <si>
-    <t>A_Marie_1_1_Antonin</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth+3, S_Marie_Regime-2</t>
-  </si>
-  <si>
-    <t>A_Marie_1_1_Mirek</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth+1</t>
-  </si>
-  <si>
-    <t>multi</t>
-  </si>
-  <si>
-    <t>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</t>
-  </si>
-  <si>
-    <t>A_Marie_1_2_Nikdo </t>
-  </si>
-  <si>
-    <t>Nikdo</t>
-  </si>
-  <si>
-    <t>A_Marie_1_2_Antonin</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime+1</t>
-  </si>
-  <si>
-    <t>A_Marie_1_2_Mirek</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth+5; S_Marie_Control+1</t>
-  </si>
-  <si>
-    <t>A_Marie_1_2_Other</t>
-  </si>
-  <si>
-    <t>_OTHER_</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>Vybrali tě za novou členku skupiny Srdce party?</t>
-  </si>
-  <si>
-    <t>Ano</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime-2</t>
-  </si>
-  <si>
-    <t>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_1_Prace</t>
-  </si>
-  <si>
-    <t>Práce</t>
-  </si>
-  <si>
-    <t>S_Antonin_Activity+1</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_1_Duchod</t>
-  </si>
-  <si>
-    <t>Důchod</t>
-  </si>
-  <si>
-    <t>S_Antonin_Activity-1</t>
-  </si>
-  <si>
-    <t>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_2_Deti</t>
-  </si>
-  <si>
-    <t>Děti</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_2_Klid</t>
-  </si>
-  <si>
-    <t>Klid</t>
-  </si>
-  <si>
-    <t>poll-answer</t>
-  </si>
-  <si>
-    <t>Q_Group_Funkcionari_Nastupce</t>
-  </si>
-  <si>
-    <t>Fotil jsi:</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_4_Funkcionare</t>
-  </si>
-  <si>
-    <t>Funkcionáře</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_4_Milovniky</t>
-  </si>
-  <si>
-    <t>Milovníky přírody</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_4_Nikoho</t>
-  </si>
-  <si>
-    <t>Block ID</t>
-  </si>
-  <si>
-    <t>Nikoho</t>
-  </si>
-  <si>
-    <t>Variation ID</t>
-  </si>
-  <si>
-    <t>Variation Description</t>
-  </si>
-  <si>
-    <t>Variation Text</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Conditions</t>
-  </si>
-  <si>
-    <t>Došlo ke sňatku Marie a Mirka?</t>
-  </si>
-  <si>
-    <t>B_Marie_1_Historie_1</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_1_A</t>
-  </si>
-  <si>
-    <t>HOUSEHOLD_CREATE(Marie, Mirek)</t>
-  </si>
-  <si>
-    <t>Antonín vede partu a Marie je radikální</t>
-  </si>
-  <si>
-    <t>scale_direct</t>
-  </si>
-  <si>
-    <t>V uplynulém roce podpořila vedení party a její postoj k režimu se zostřil.</t>
-  </si>
-  <si>
-    <t>Nastav Mirkovu hodnotu Regime po poradě orgů.</t>
-  </si>
-  <si>
-    <t>A_Organizatori_1_2_Nastaveni</t>
-  </si>
-  <si>
-    <t>Nová hodnota</t>
-  </si>
-  <si>
-    <t>A_Marie_1_1_Antonin AND S_Marie_Regime &gt;= 5</t>
-  </si>
-  <si>
-    <t>S_Mirek_Regime=VALUE</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_1_B</t>
-  </si>
-  <si>
-    <t>resource_direct</t>
-  </si>
-  <si>
-    <t>Antonín vede partu, nikdo jí nepomáhá</t>
-  </si>
-  <si>
-    <t>Nastav osobní účet Antonína po poradě orgů.</t>
-  </si>
-  <si>
-    <t>Vedení party přijala s rezervou a o pomoc s Ekofilmem nikoho nepožádala.</t>
-  </si>
-  <si>
-    <t>A_Organizatori_1_3_Nastaveni</t>
-  </si>
-  <si>
-    <t>A_Marie_1_1_Antonin AND !(A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
-  </si>
-  <si>
-    <t>R_Antonin_Wealth_private=VALUE</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_1_C</t>
-  </si>
-  <si>
-    <t>Náhoda 50 %</t>
-  </si>
-  <si>
-    <t>poll</t>
-  </si>
-  <si>
-    <t>V uplynulém roce si pořídila kocoura.</t>
-  </si>
-  <si>
-    <t>Kdo by se podle tebe měl stát novým vedoucím směny?</t>
-  </si>
-  <si>
-    <t>A_Group_Funkcionari_Nastupce_Antonin</t>
-  </si>
-  <si>
-    <t>!A_Marie_1_1_Antonin AND RANDOM(50)</t>
-  </si>
-  <si>
-    <t>Antonín Hájek</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_1_D</t>
-  </si>
-  <si>
-    <t>A_Group_Funkcionari_Nastupce_Mirek</t>
-  </si>
-  <si>
-    <t>Dobře se jí daří — text záměrně prázdný (nic se nestalo)</t>
-  </si>
-  <si>
-    <t>Mirek Pokorný</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth &gt;= 7</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_1_E</t>
-  </si>
-  <si>
-    <t>Fallback + zanořený blok</t>
-  </si>
-  <si>
-    <t>Rok proběhl bez zásadních změn. {BLOK B_Marie_1_Historie_2}</t>
-  </si>
-  <si>
-    <t>DEFAULT</t>
-  </si>
-  <si>
-    <t>B_Marie_1_Historie_2</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_2_A</t>
-  </si>
-  <si>
-    <t>Přijata do Srdce party</t>
-  </si>
-  <si>
-    <t>Byla přijata do Srdce party.</t>
-  </si>
-  <si>
-    <t>A_Marie_1_3_Ano</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_2_B</t>
-  </si>
-  <si>
-    <t>Nepřijata (odpověď Ne bez řádku v listu)</t>
-  </si>
-  <si>
-    <t>Do Srdce party přijata nebyla.</t>
-  </si>
-  <si>
-    <t>A_Marie_1_3_Ne</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Historie_2_C</t>
-  </si>
-  <si>
-    <t>Fallback s prázdnou podmínkou i textem</t>
-  </si>
-  <si>
-    <t>B_Marie_1_Questions_1</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Questions_1_A</t>
-  </si>
-  <si>
-    <t>Bez priority — rozhoduje pořadí řádků</t>
-  </si>
-  <si>
-    <t>Doplňující otázka A pro další kapitolu.</t>
-  </si>
-  <si>
-    <t>!A_Marie_1_1_Antonin</t>
-  </si>
-  <si>
-    <t>V_Marie_1_Questions_1_B</t>
-  </si>
-  <si>
-    <t>Fallback (prázdná podmínka)</t>
-  </si>
-  <si>
-    <t>Doplňující otázka B pro další kapitolu.</t>
-  </si>
-  <si>
-    <t>B_Antonin_1_Historie_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_1_A</t>
-  </si>
-  <si>
-    <t>Je plně v důchodu</t>
-  </si>
-  <si>
-    <t>Je plně v důchodu.</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_1_B</t>
-  </si>
-  <si>
-    <t>Pracuje jako vrátný</t>
-  </si>
-  <si>
-    <t>Pracuje jako vrátný při důchodu.</t>
-  </si>
-  <si>
-    <t>B_Antonin_1_Historie_2</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_2_A</t>
-  </si>
-  <si>
-    <t>Vedoucím směny se stal Mirek</t>
-  </si>
-  <si>
-    <t>Vedoucím směny se stal mladší kolega.</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_2_B</t>
-  </si>
-  <si>
-    <t>Zůstává on</t>
-  </si>
-  <si>
-    <t>Vedoucím směny zůstal on sám.</t>
-  </si>
-  <si>
-    <t>B_Antonin_1_Historie_3</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_3_C</t>
-  </si>
-  <si>
-    <t>Fallback stojí na řádku první, ale má nejvyšší číslo</t>
-  </si>
-  <si>
-    <t>Rok byl klidný.</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_3_A</t>
-  </si>
-  <si>
-    <t>Aktivní + hlídá děti</t>
-  </si>
-  <si>
-    <t>Rok byl plný práce a hlídání dětí v okolí.</t>
-  </si>
-  <si>
-    <t>A_Antonin_1_2_Deti AND S_Antonin_Activity &gt;= 5</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Historie_3_B</t>
-  </si>
-  <si>
-    <t>Aktivní</t>
-  </si>
-  <si>
-    <t>Rok byl plný práce.</t>
-  </si>
-  <si>
-    <t>S_Antonin_Activity &gt;= 5</t>
-  </si>
-  <si>
-    <t>B_Antonin_1_Foto_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Foto_1_A</t>
-  </si>
-  <si>
-    <t>Fotil funkcionáře</t>
-  </si>
-  <si>
-    <t>Fotil funkcionáře.</t>
-  </si>
-  <si>
-    <t>V_Antonin_1_Foto_1_B</t>
-  </si>
-  <si>
-    <t>Fotil něco jiného.</t>
-  </si>
-  <si>
-    <t>B_Mirek_1_Historie_1</t>
-  </si>
-  <si>
-    <t>V_Mirek_1_Historie_1_A</t>
-  </si>
-  <si>
-    <t>Vyhrál anketu</t>
-  </si>
-  <si>
-    <t>Stal se vedoucím směny.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A_Group_Funkcionari_Nastupce_Mirek
-</t>
-  </si>
-  <si>
-    <t>V_Mirek_1_Historie_1_B</t>
-  </si>
-  <si>
-    <t>Fallback</t>
-  </si>
-  <si>
-    <t>Vedoucím směny se nestal.</t>
-  </si>
-  <si>
-    <t>B_Funkcionari_1_Vedeni_1</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_1_Vedeni_1_A</t>
-  </si>
-  <si>
-    <t>Nový vedoucí Mirek</t>
-  </si>
-  <si>
-    <t>Vedení převzal mladší člen.</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_1_Vedeni_1_B</t>
-  </si>
-  <si>
-    <t>Vedení zůstalo beze změny.</t>
-  </si>
-  <si>
-    <t>B_SrdceParty_1_Clenove_1</t>
-  </si>
-  <si>
-    <t>V_SrdceParty_1_Clenove_1_A</t>
-  </si>
-  <si>
-    <t>Marie přijata</t>
-  </si>
-  <si>
-    <t>Skupina přijala nového člena.</t>
-  </si>
-  <si>
-    <t>V_SrdceParty_1_Clenove_1_B</t>
-  </si>
-  <si>
-    <t>Složení skupiny se nezměnilo.</t>
-  </si>
-  <si>
-    <t>Condition</t>
-  </si>
-  <si>
-    <t>B_Marie_2_Historie_1</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_A</t>
-  </si>
-  <si>
-    <t>Vystoupila veřejně</t>
-  </si>
-  <si>
-    <t>Veřejně vystoupila proti režimu.</t>
-  </si>
-  <si>
-    <t>A_Marie_2_2_Ano</t>
-  </si>
-  <si>
-    <t>Podaří se Marii zorganizovat lokální verzi Ekofilmu? Kdo přislíbil pomoc?</t>
-  </si>
-  <si>
-    <t>A_Marie_2_1_Nikdo</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_B</t>
-  </si>
-  <si>
-    <t>Přispěla na fond</t>
-  </si>
-  <si>
-    <t>Přispěla na stávkový fond a zbylo jí dost peněz.</t>
-  </si>
-  <si>
-    <t>A_Marie_2_1_Antonin</t>
-  </si>
-  <si>
-    <t>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</t>
-  </si>
-  <si>
-    <t>S_Marie_Control+1</t>
-  </si>
-  <si>
-    <t>V_Marie_2_Historie_1_C</t>
-  </si>
-  <si>
-    <t>A_Marie_2_1_Mirek</t>
-  </si>
-  <si>
-    <t>Držela se v ústraní.</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth+2</t>
-  </si>
-  <si>
-    <t>A_Marie_2_1_Other</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Auto_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_1_A</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime &gt;= 5 AND (A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
-  </si>
-  <si>
-    <t>Auto dostal Mirek</t>
-  </si>
-  <si>
-    <t>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</t>
-  </si>
-  <si>
-    <t>Vystoupíš veřejně proti režimu?</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_1_Mirek</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime+2, S_Marie_Control-1</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_1_B</t>
-  </si>
-  <si>
-    <t>Ne</t>
-  </si>
-  <si>
-    <t>Auto si nechal.</t>
-  </si>
-  <si>
-    <t>Přispěješ na stávkový fond?</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Auto_2</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_2_A</t>
-  </si>
-  <si>
-    <t>R_Marie_Wealth_private-3</t>
-  </si>
-  <si>
-    <t>Poslední projížďka</t>
-  </si>
-  <si>
-    <t>Před předáním se s ním naposled projel.</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_2_Ano</t>
-  </si>
-  <si>
-    <t>Komu daruješ automobil s garáží?</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Auto_2_B</t>
-  </si>
-  <si>
-    <t>R_Antonin_Wealth-10, R_Mirek_Wealth+10</t>
-  </si>
-  <si>
-    <t>Fallback — nic se nestalo</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_1_Nikdo</t>
-  </si>
-  <si>
-    <t>Nikomu</t>
-  </si>
-  <si>
-    <t>B_Antonin_2_Stavka_1</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_A</t>
-  </si>
-  <si>
-    <t>Podpořil stávku</t>
-  </si>
-  <si>
-    <t>Stávku veřejně podpořil.</t>
-  </si>
-  <si>
-    <t>Podpoříš veřejně ekologickou stávku v podniku?</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_B</t>
-  </si>
-  <si>
-    <t>Nepodpořil</t>
-  </si>
-  <si>
-    <t>Ke stávce se nepřidal.</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_2_Ne</t>
-  </si>
-  <si>
-    <t>V_Antonin_2_Stavka_1_C</t>
-  </si>
-  <si>
-    <t>Fallback — otázka se nekladla</t>
-  </si>
-  <si>
-    <t>Stávka se ho netýkala.</t>
-  </si>
-  <si>
-    <t>B_Funkcionari_2_Vedeni_1</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Vedeni_1_A</t>
-  </si>
-  <si>
-    <t>Aktivní vedení</t>
-  </si>
-  <si>
-    <t>Vedení bylo aktivní.</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Vedeni_1_B</t>
-  </si>
-  <si>
-    <t>Kdo má nést odpovědnost za nesrovnalosti ve skladu materiálu?</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_3_Mirek</t>
-  </si>
-  <si>
-    <t>Vedení bylo pasivní.</t>
-  </si>
-  <si>
-    <t>A_Antonin_2_3_Nikdo</t>
-  </si>
-  <si>
-    <t>B_Funkcionari_2_Zapis_1</t>
-  </si>
-  <si>
-    <t>V_Funkcionari_2_Zapis_1_A</t>
-  </si>
-  <si>
-    <t>Jediná varianta = fallback</t>
-  </si>
-  <si>
-    <t>Zápis ze schůze byl archivován.</t>
-  </si>
-  <si>
-    <t>Došlo k rozvodu Marie a Mirka?</t>
-  </si>
-  <si>
-    <t>HOUSEHOLD_DELETE(Marie, Mirek)</t>
-  </si>
-  <si>
-    <t>Vstoupila jsi do nové strany?</t>
-  </si>
-  <si>
-    <t>S_Marie_Regime-1</t>
-  </si>
-  <si>
-    <t>Vrátíš se do zaměstnání?</t>
-  </si>
-  <si>
-    <t>A_Antonin_3_1_Vratim</t>
-  </si>
-  <si>
-    <t>Vrátím se</t>
-  </si>
-  <si>
-    <t>A_Antonin_3_1_Zustanu</t>
-  </si>
-  <si>
-    <t>Zůstanu v důchodu</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7E6E6"/>
-        <bgColor rgb="FFE7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0D0D0"/>
-        <bgColor rgb="FFD0D0D0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCCC"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
-    <border/>
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-    </border>
-    <border>
-      <left/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <top/>
-      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1222,29 +279,50 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="110.0"/>
-    <col customWidth="1" min="2" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="110"/>
+    <col min="2" max="2" customWidth="1" width="8.71"/>
+    <col min="3" max="3" customWidth="1" width="8.71"/>
+    <col min="4" max="4" customWidth="1" width="8.71"/>
+    <col min="5" max="5" customWidth="1" width="8.71"/>
+    <col min="6" max="6" customWidth="1" width="8.71"/>
+    <col min="7" max="7" customWidth="1" width="8.71"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" t="str">
+        <v>Fixture — platný (testovací data, ne skutečná hra)</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2228,130 +1306,136 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="44.0"/>
-    <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="4" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="60.0"/>
-    <col customWidth="1" min="6" max="6" width="36.0"/>
-    <col customWidth="1" min="7" max="7" width="28.0"/>
-    <col customWidth="1" min="8" max="8" width="52.0"/>
-    <col customWidth="1" min="9" max="9" width="18.0"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="44"/>
+    <col min="3" max="3" customWidth="1" width="18"/>
+    <col min="4" max="4" customWidth="1" width="13"/>
+    <col min="5" max="5" customWidth="1" width="60"/>
+    <col min="6" max="6" customWidth="1" width="36"/>
+    <col min="7" max="7" customWidth="1" width="28"/>
+    <col min="8" max="8" customWidth="1" width="52"/>
+    <col min="9" max="9" customWidth="1" width="18"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>39</v>
+      <c r="C1" t="str">
+        <v>Questions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Responses</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Scale and Resources Impact</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Effects</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="A2" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Condition</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Text</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ID Answer</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Text response</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>271</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="D3" t="str">
+        <v>bool</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Vstoupila jsi do nové strany?</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="H3" t="str">
+        <v>S_Marie_Regime-1</v>
       </c>
     </row>
     <row r="4">
-      <c r="G4" s="10" t="s">
-        <v>228</v>
+      <c r="G4" t="str">
+        <v>Ne</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>68</v>
+      <c r="A5" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B5" t="str">
+        <v>S_Antonin_Activity &gt;= 5</v>
+      </c>
+      <c r="D5" t="str">
+        <v>single</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Vrátíš se do zaměstnání?</v>
+      </c>
+      <c r="F5" t="str">
+        <v>A_Antonin_3_1_Vratim</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Vrátím se</v>
+      </c>
+      <c r="H5" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="6">
-      <c r="F6" s="8" t="s">
-        <v>275</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>71</v>
+      <c r="F6" t="str">
+        <v>A_Antonin_3_1_Zustanu</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Zůstanu v důchodu</v>
+      </c>
+      <c r="H6" t="str">
+        <v>S_Antonin_Activity-1</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3339,87 +2423,103 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="4" width="22.29"/>
-    <col customWidth="1" min="5" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="18"/>
+    <col min="3" max="3" customWidth="1" width="18"/>
+    <col min="4" max="4" customWidth="1" width="22.29"/>
+    <col min="5" max="5" customWidth="1" width="8.71"/>
+    <col min="6" max="6" customWidth="1" width="8.71"/>
+    <col min="7" max="7" customWidth="1" width="8.71"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="5"/>
+      <c r="A1" t="str">
+        <v>Characters</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>19</v>
+      <c r="A2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Surname</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Household</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>25</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Balážová</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>27</v>
+      <c r="A4" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Antonín</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Hájek</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>29</v>
+      <c r="A5" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="B5" t="str">
+        <v xml:space="preserve"> Mirek</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Pokorný</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>31</v>
+      <c r="A6" t="str">
+        <v>Organizatori</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Organizátoři</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4406,53 +3506,70 @@
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="24" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="18"/>
+    <col min="3" max="3" customWidth="1" width="8.71"/>
+    <col min="4" max="4" customWidth="1" width="8.71"/>
+    <col min="5" max="5" customWidth="1" width="8.71"/>
+    <col min="6" max="6" customWidth="1" width="8.71"/>
+    <col min="7" max="7" customWidth="1" width="8.71"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="5"/>
+      <c r="A1" t="str">
+        <v>Groups</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>8</v>
+      <c r="A2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Name</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>13</v>
+      <c r="A3" t="str">
+        <v>Funkcionari</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Funkcionáři</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>16</v>
+      <c r="A4" t="str">
+        <v>SrdceParty</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Srdce party</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5439,116 +4556,130 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="4" width="8.0"/>
-    <col customWidth="1" min="5" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="24"/>
+    <col min="3" max="3" customWidth="1" width="8"/>
+    <col min="4" max="4" customWidth="1" width="8"/>
+    <col min="5" max="5" customWidth="1" width="10"/>
+    <col min="6" max="6" customWidth="1" width="8.71"/>
+    <col min="7" max="7" customWidth="1" width="8.71"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5"/>
+      <c r="B1" t="str">
+        <v>Scales</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>12</v>
+      <c r="A2" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Min</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Max</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Default</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>1.0</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>S_Marie_Regime</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="E4" s="8">
-        <v>5.0</v>
+      <c r="B4" t="str">
+        <v xml:space="preserve">S_Marie_Control </v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="8">
-        <v>8.0</v>
-      </c>
-      <c r="E5" s="8">
-        <v>4.0</v>
+      <c r="A5" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B5" t="str">
+        <v>S_Antonin_Activity</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="E6" s="8">
-        <v>3.0</v>
+      <c r="A6" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="B6" t="str">
+        <v>S_Mirek_Regime</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6535,75 +5666,92 @@
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="24.0"/>
-    <col customWidth="1" min="3" max="3" width="10.0"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="24"/>
+    <col min="3" max="3" customWidth="1" width="10"/>
+    <col min="4" max="4" customWidth="1" width="8.71"/>
+    <col min="5" max="5" customWidth="1" width="8.71"/>
+    <col min="6" max="6" customWidth="1" width="8.71"/>
+    <col min="7" max="7" customWidth="1" width="8.71"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="5"/>
+      <c r="B1" t="str">
+        <v>Resources</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>12</v>
+      <c r="A2" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Default</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="8">
-        <v>10.0</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>R_Marie_Wealth</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="8">
-        <v>50.0</v>
+      <c r="A4" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B4" t="str">
+        <v>R_Antonin_Wealth</v>
+      </c>
+      <c r="C4">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="8">
-        <v>20.0</v>
+      <c r="A5" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="B5" t="str">
+        <v>R_Mirek_Wealth</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -7590,356 +6738,363 @@
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="18.0"/>
-    <col customWidth="1" min="3" max="3" width="13.0"/>
-    <col customWidth="1" min="4" max="4" width="60.0"/>
-    <col customWidth="1" min="5" max="5" width="36.0"/>
-    <col customWidth="1" min="6" max="6" width="28.0"/>
-    <col customWidth="1" min="7" max="7" width="46.0"/>
-    <col customWidth="1" min="8" max="8" width="18.0"/>
-    <col customWidth="1" min="9" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="18"/>
+    <col min="3" max="3" customWidth="1" width="13"/>
+    <col min="4" max="4" customWidth="1" width="60"/>
+    <col min="5" max="5" customWidth="1" width="36"/>
+    <col min="6" max="6" customWidth="1" width="28"/>
+    <col min="7" max="7" customWidth="1" width="46"/>
+    <col min="8" max="8" customWidth="1" width="18"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
+      <c r="B1" t="str">
+        <v>Questions</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Responses</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Scale and Resources Impact</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Effects</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
+      <c r="A2" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Text</v>
+      </c>
+      <c r="E2" t="str">
+        <v>ID Answer</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Text response</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>48</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Q_Marie_1_1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>single</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Kdo by měl vést partu ochránců přírody?</v>
+      </c>
+      <c r="E3" t="str">
+        <v>A_Marie_1_1_Antonin</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Antonín</v>
+      </c>
+      <c r="G3" t="str">
+        <v>R_Marie_Wealth+3, S_Marie_Regime-2</v>
       </c>
     </row>
     <row r="4">
-      <c r="E4" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>50</v>
+      <c r="E4" t="str">
+        <v>A_Marie_1_1_Mirek</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="G4" t="str">
+        <v>R_Marie_Wealth+1</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>54</v>
+      <c r="C5" t="str">
+        <v>multi</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</v>
+      </c>
+      <c r="E5" t="str">
+        <v xml:space="preserve">A_Marie_1_2_Nikdo </v>
+      </c>
+      <c r="F5" t="str">
+        <v>Nikdo</v>
       </c>
     </row>
     <row r="6">
-      <c r="E6" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>56</v>
+      <c r="E6" t="str">
+        <v>A_Marie_1_2_Antonin</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Antonín</v>
+      </c>
+      <c r="G6" t="str">
+        <v>S_Marie_Regime+1</v>
       </c>
     </row>
     <row r="7">
-      <c r="E7" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>58</v>
+      <c r="E7" t="str">
+        <v>A_Marie_1_2_Mirek</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="G7" t="str">
+        <v>R_Marie_Wealth+5; S_Marie_Control+1</v>
       </c>
     </row>
     <row r="8">
-      <c r="E8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>60</v>
+      <c r="E8" t="str">
+        <v>A_Marie_1_2_Other</v>
+      </c>
+      <c r="F8" t="str">
+        <v>_OTHER_</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>64</v>
+      <c r="C9" t="str">
+        <v>bool</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Vybrali tě za novou členku skupiny Srdce party?</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="G9" t="str">
+        <v>S_Marie_Regime-2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>68</v>
+      <c r="A10" t="str">
+        <v>Antonín</v>
+      </c>
+      <c r="C10" t="str">
+        <v>single</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</v>
+      </c>
+      <c r="E10" t="str">
+        <v>A_Antonin_1_1_Prace</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Práce</v>
+      </c>
+      <c r="G10" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="11">
-      <c r="E11" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>71</v>
+      <c r="E11" t="str">
+        <v>A_Antonin_1_1_Duchod</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Důchod</v>
+      </c>
+      <c r="G11" t="str">
+        <v>S_Antonin_Activity-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>68</v>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</v>
+      </c>
+      <c r="E12" t="str">
+        <v>A_Antonin_1_2_Deti</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Děti</v>
+      </c>
+      <c r="G12" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="13">
-      <c r="E13" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>71</v>
+      <c r="E13" t="str">
+        <v>A_Antonin_1_2_Klid</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Klid</v>
+      </c>
+      <c r="G13" t="str">
+        <v>S_Antonin_Activity-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>78</v>
+      <c r="C14" t="str">
+        <v>poll-answer</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Q_Group_Funkcionari_Nastupce</v>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>68</v>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Fotil jsi:</v>
+      </c>
+      <c r="E15" t="str">
+        <v>A_Antonin_1_4_Funkcionare</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Funkcionáře</v>
+      </c>
+      <c r="G15" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="16">
-      <c r="E16" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>68</v>
+      <c r="E16" t="str">
+        <v>A_Antonin_1_4_Milovniky</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Milovníky přírody</v>
+      </c>
+      <c r="G16" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="17">
-      <c r="E17" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>71</v>
+      <c r="E17" t="str">
+        <v>A_Antonin_1_4_Nikoho</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Nikoho</v>
+      </c>
+      <c r="G17" t="str">
+        <v>S_Antonin_Activity-1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>78</v>
+      <c r="A18" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="C18" t="str">
+        <v>poll-answer</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Q_Group_Funkcionari_Nastupce</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="12" t="s">
-        <v>95</v>
+      <c r="A19" t="str">
+        <v>Organizatori</v>
+      </c>
+      <c r="C19" t="str">
+        <v>bool</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Došlo ke sňatku Marie a Mirka?</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="H19" t="str">
+        <v>HOUSEHOLD_CREATE(Marie, Mirek)</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>103</v>
+      <c r="C20" t="str">
+        <v>scale_direct</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Nastav Mirkovu hodnotu Regime po poradě orgů.</v>
+      </c>
+      <c r="E20" t="str">
+        <v>A_Organizatori_1_2_Nastaveni</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Nová hodnota</v>
+      </c>
+      <c r="G20" t="str">
+        <v>S_Mirek_Regime=VALUE</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="C21" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>111</v>
+      <c r="C21" t="str">
+        <v>resource_direct</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Nastav osobní účet Antonína po poradě orgů.</v>
+      </c>
+      <c r="E21" t="str">
+        <v>A_Organizatori_1_3_Nastaveni</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Nová hodnota</v>
+      </c>
+      <c r="G21" t="str">
+        <v>R_Antonin_Wealth_private=VALUE</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="B23" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>119</v>
+      <c r="B23" t="str">
+        <v>Q_Group_Funkcionari_Nastupce</v>
+      </c>
+      <c r="C23" t="str">
+        <v>poll</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Kdo by se podle tebe měl stát novým vedoucím směny?</v>
+      </c>
+      <c r="E23" t="str">
+        <v>A_Group_Funkcionari_Nastupce_Antonin</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Antonín Hájek</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>123</v>
+      <c r="E24" t="str">
+        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Mirek Pokorný</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -8923,500 +8078,516 @@
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:F1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="28.0"/>
-    <col customWidth="1" min="3" max="3" width="32.0"/>
-    <col customWidth="1" min="4" max="4" width="40.0"/>
-    <col customWidth="1" min="5" max="5" width="60.0"/>
-    <col customWidth="1" min="6" max="6" width="9.0"/>
-    <col customWidth="1" min="7" max="7" width="52.0"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="28"/>
+    <col min="3" max="3" customWidth="1" width="32"/>
+    <col min="4" max="4" customWidth="1" width="40"/>
+    <col min="5" max="5" customWidth="1" width="60"/>
+    <col min="6" max="6" customWidth="1" width="9"/>
+    <col min="7" max="7" customWidth="1" width="52"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>91</v>
+      <c r="A1" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Block ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Variation ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Variation Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Variation Text</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Conditions</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>102</v>
+      <c r="A2" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B2" t="str">
+        <v>B_Marie_1_Historie_1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>V_Marie_1_Historie_1_A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Antonín vede partu a Marie je radikální</v>
+      </c>
+      <c r="E2" t="str">
+        <v>V uplynulém roce podpořila vedení party a její postoj k režimu se zostřil.</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>A_Marie_1_1_Antonin AND S_Marie_Regime &gt;= 5</v>
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>110</v>
+      <c r="C3" t="str">
+        <v>V_Marie_1_Historie_1_B</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Antonín vede partu, nikdo jí nepomáhá</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Vedení party přijala s rezervou a o pomoc s Ekofilmem nikoho nepožádala.</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A_Marie_1_1_Antonin AND !(A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="F4" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>118</v>
+      <c r="C4" t="str">
+        <v>V_Marie_1_Historie_1_C</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Náhoda 50 %</v>
+      </c>
+      <c r="E4" t="str">
+        <v>V uplynulém roce si pořídila kocoura.</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>!A_Marie_1_1_Antonin AND RANDOM(50)</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="8">
-        <v>4.0</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>124</v>
+      <c r="C5" t="str">
+        <v>V_Marie_1_Historie_1_D</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Dobře se jí daří — text záměrně prázdný (nic se nestalo)</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="str">
+        <v>R_Marie_Wealth &gt;= 7</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="F6" s="8">
-        <v>5.0</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>128</v>
+      <c r="C6" t="str">
+        <v>V_Marie_1_Historie_1_E</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Fallback + zanořený blok</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Rok proběhl bez zásadních změn. {BLOK B_Marie_1_Historie_2}</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>133</v>
+      <c r="B7" t="str">
+        <v>B_Marie_1_Historie_2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>V_Marie_1_Historie_2_A</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Přijata do Srdce party</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Byla přijata do Srdce party.</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>A_Marie_1_3_Ano</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="F8" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>137</v>
+      <c r="C8" t="str">
+        <v>V_Marie_1_Historie_2_B</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Nepřijata (odpověď Ne bez řádku v listu)</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Do Srdce party přijata nebyla.</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="str">
+        <v>A_Marie_1_3_Ne</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="F9" s="8">
-        <v>3.0</v>
+      <c r="C9" t="str">
+        <v>V_Marie_1_Historie_2_C</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Fallback s prázdnou podmínkou i textem</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" s="13" t="s">
-        <v>144</v>
+      <c r="B10" t="str">
+        <v>B_Marie_1_Questions_1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>V_Marie_1_Questions_1_A</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Bez priority — rozhoduje pořadí řádků</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Doplňující otázka A pro další kapitolu.</v>
+      </c>
+      <c r="G10" t="str">
+        <v>!A_Marie_1_1_Antonin</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>147</v>
+      <c r="C11" t="str">
+        <v>V_Marie_1_Questions_1_B</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Fallback (prázdná podmínka)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Doplňující otázka B pro další kapitolu.</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>69</v>
+      <c r="A12" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B_Antonin_1_Historie_1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>V_Antonin_1_Historie_1_A</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Je plně v důchodu</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Je plně v důchodu.</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>A_Antonin_1_1_Duchod</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>128</v>
+      <c r="C13" t="str">
+        <v>V_Antonin_1_Historie_1_B</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Pracuje jako vrátný</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Pracuje jako vrátný při důchodu.</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="F14" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>121</v>
+      <c r="B14" t="str">
+        <v>B_Antonin_1_Historie_2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>V_Antonin_1_Historie_2_A</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Vedoucím směny se stal Mirek</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Vedoucím směny se stal mladší kolega.</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="F15" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>128</v>
+      <c r="C15" t="str">
+        <v>V_Antonin_1_Historie_2_B</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Zůstává on</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Vedoucím směny zůstal on sám.</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>128</v>
+      <c r="B16" t="str">
+        <v>B_Antonin_1_Historie_3</v>
+      </c>
+      <c r="C16" t="str">
+        <v>V_Antonin_1_Historie_3_C</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Fallback stojí na řádku první, ale má nejvyšší číslo</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Rok byl klidný.</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="17">
-      <c r="C17" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>169</v>
+      <c r="C17" t="str">
+        <v>V_Antonin_1_Historie_3_A</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Aktivní + hlídá děti</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Rok byl plný práce a hlídání dětí v okolí.</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>A_Antonin_1_2_Deti AND S_Antonin_Activity &gt;= 5</v>
       </c>
     </row>
     <row r="18">
-      <c r="C18" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F18" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>173</v>
+      <c r="C18" t="str">
+        <v>V_Antonin_1_Historie_3_B</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Aktivní</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Rok byl plný práce.</v>
+      </c>
+      <c r="F18">
+        <v>2</v>
+      </c>
+      <c r="G18" t="str">
+        <v>S_Antonin_Activity &gt;= 5</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>80</v>
+      <c r="B19" t="str">
+        <v>B_Antonin_1_Foto_1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>V_Antonin_1_Foto_1_A</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Fotil funkcionáře</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Fotil funkcionáře.</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>A_Antonin_1_4_Funkcionare</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="8">
-        <v>2.0</v>
+      <c r="C20" t="str">
+        <v>V_Antonin_1_Foto_1_B</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Fallback (prázdná podmínka)</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Fotil něco jiného.</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>184</v>
+    <row r="21" ht="15.75" customHeight="1" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="B21" t="str">
+        <v>B_Mirek_1_Historie_1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>V_Mirek_1_Historie_1_A</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Vyhrál anketu</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Stal se vedoucím směny.</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="str" xml:space="preserve">
+        <v xml:space="preserve">A_Group_Funkcionari_Nastupce_Mirek
+</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="C22" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>128</v>
+      <c r="C22" t="str">
+        <v>V_Mirek_1_Historie_1_B</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Vedoucím směny se nestal.</v>
+      </c>
+      <c r="F22">
+        <v>2</v>
+      </c>
+      <c r="G22" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="F23" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>121</v>
+      <c r="A23" t="str">
+        <v>Funkcionari</v>
+      </c>
+      <c r="B23" t="str">
+        <v>B_Funkcionari_1_Vedeni_1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>V_Funkcionari_1_Vedeni_1_A</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Nový vedoucí Mirek</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Vedení převzal mladší člen.</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="str">
+        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F24" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>128</v>
+      <c r="C24" t="str">
+        <v>V_Funkcionari_1_Vedeni_1_B</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Vedení zůstalo beze změny.</v>
+      </c>
+      <c r="F24">
+        <v>2</v>
+      </c>
+      <c r="G24" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="F25" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>133</v>
+      <c r="A25" t="str">
+        <v>SrdceParty</v>
+      </c>
+      <c r="B25" t="str">
+        <v>B_SrdceParty_1_Clenove_1</v>
+      </c>
+      <c r="C25" t="str">
+        <v>V_SrdceParty_1_Clenove_1_A</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Marie přijata</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Skupina přijala nového člena.</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="str">
+        <v>A_Marie_1_3_Ano</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>199</v>
-      </c>
-      <c r="F26" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>128</v>
+      <c r="C26" t="str">
+        <v>V_SrdceParty_1_Clenove_1_B</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Složení skupiny se nezměnilo.</v>
+      </c>
+      <c r="F26">
+        <v>2</v>
+      </c>
+      <c r="G26" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -10394,265 +9565,270 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="44.0"/>
-    <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="4" width="13.0"/>
-    <col customWidth="1" min="5" max="5" width="60.0"/>
-    <col customWidth="1" min="6" max="6" width="36.0"/>
-    <col customWidth="1" min="7" max="7" width="28.0"/>
-    <col customWidth="1" min="8" max="8" width="52.0"/>
-    <col customWidth="1" min="9" max="9" width="18.0"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="44"/>
+    <col min="3" max="3" customWidth="1" width="18"/>
+    <col min="4" max="4" customWidth="1" width="13"/>
+    <col min="5" max="5" customWidth="1" width="60"/>
+    <col min="6" max="6" customWidth="1" width="36"/>
+    <col min="7" max="7" customWidth="1" width="28"/>
+    <col min="8" max="8" customWidth="1" width="52"/>
+    <col min="9" max="9" customWidth="1" width="18"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>39</v>
+      <c r="C1" t="str">
+        <v>Questions</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Responses</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Scale and Resources Impact</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Effects</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="A2" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Condition</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ID</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Type</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Text</v>
+      </c>
+      <c r="F2" t="str">
+        <v>ID Answer</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Text response</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>206</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>54</v>
+      <c r="A3" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B3" t="str">
+        <v>!A_Marie_1_1_Antonin</v>
+      </c>
+      <c r="D3" t="str">
+        <v>multi</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Podaří se Marii zorganizovat lokální verzi Ekofilmu? Kdo přislíbil pomoc?</v>
+      </c>
+      <c r="F3" t="str">
+        <v>A_Marie_2_1_Nikdo</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Nikdo</v>
       </c>
     </row>
     <row r="4">
-      <c r="F4" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>213</v>
+      <c r="F4" t="str">
+        <v>A_Marie_2_1_Antonin</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Antonín</v>
+      </c>
+      <c r="H4" t="str">
+        <v>S_Marie_Control+1</v>
       </c>
     </row>
     <row r="5">
-      <c r="F5" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>217</v>
+      <c r="F5" t="str">
+        <v>A_Marie_2_1_Mirek</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="H5" t="str">
+        <v>R_Marie_Wealth+2</v>
       </c>
     </row>
     <row r="6">
-      <c r="F6" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>60</v>
+      <c r="F6" t="str">
+        <v>A_Marie_2_1_Other</v>
+      </c>
+      <c r="G6" t="str">
+        <v>_OTHER_</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>226</v>
+      <c r="B7" t="str">
+        <v>S_Marie_Regime &gt;= 5 AND (A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</v>
+      </c>
+      <c r="D7" t="str">
+        <v>bool</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Vystoupíš veřejně proti režimu?</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="H7" t="str">
+        <v>S_Marie_Regime+2, S_Marie_Control-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="10" t="s">
-        <v>228</v>
+      <c r="G8" t="str">
+        <v>Ne</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>233</v>
+      <c r="B9" t="str">
+        <v>R_Marie_Wealth &gt;= 7</v>
+      </c>
+      <c r="D9" t="str">
+        <v>bool</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Přispěješ na stávkový fond?</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="H9" t="str">
+        <v>R_Marie_Wealth_private-3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>239</v>
+      <c r="A10" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="D10" t="str">
+        <v>single</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Komu daruješ automobil s garáží?</v>
+      </c>
+      <c r="F10" t="str">
+        <v>A_Antonin_2_1_Mirek</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Mirek</v>
+      </c>
+      <c r="H10" t="str">
+        <v>R_Antonin_Wealth-10, R_Mirek_Wealth+10</v>
       </c>
     </row>
     <row r="11">
-      <c r="F11" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>242</v>
+      <c r="F11" t="str">
+        <v>A_Antonin_2_1_Nikdo</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Nikomu</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>68</v>
+      <c r="B12" t="str">
+        <v>A_Antonin_1_1_Prace</v>
+      </c>
+      <c r="D12" t="str">
+        <v>bool</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Podpoříš veřejně ekologickou stávku v podniku?</v>
+      </c>
+      <c r="F12" t="str">
+        <v>A_Antonin_2_2_Ano</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="H12" t="str">
+        <v>S_Antonin_Activity+1</v>
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>71</v>
+      <c r="F13" t="str">
+        <v>A_Antonin_2_2_Ne</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Ne</v>
+      </c>
+      <c r="H13" t="str">
+        <v>S_Antonin_Activity-1</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>23</v>
+      <c r="B14" t="str">
+        <v>DEFAULT</v>
+      </c>
+      <c r="D14" t="str">
+        <v>single</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Kdo má nést odpovědnost za nesrovnalosti ve skladu materiálu?</v>
+      </c>
+      <c r="F14" t="str">
+        <v>A_Antonin_2_3_Mirek</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Mirek</v>
       </c>
     </row>
     <row r="15">
-      <c r="F15" s="8" t="s">
-        <v>263</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>54</v>
+      <c r="F15" t="str">
+        <v>A_Antonin_2_3_Nikdo</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Nikdo</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="12" t="s">
-        <v>269</v>
+      <c r="A16" t="str">
+        <v>Organizatori</v>
+      </c>
+      <c r="D16" t="str">
+        <v>bool</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Došlo k rozvodu Marie a Mirka?</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Ano</v>
+      </c>
+      <c r="I16" t="str">
+        <v>HOUSEHOLD_DELETE(Marie, Mirek)</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -11640,290 +10816,305 @@
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1000"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="28.0"/>
-    <col customWidth="1" min="3" max="3" width="32.0"/>
-    <col customWidth="1" min="4" max="4" width="40.0"/>
-    <col customWidth="1" min="5" max="5" width="60.0"/>
-    <col customWidth="1" min="6" max="6" width="9.0"/>
-    <col customWidth="1" min="7" max="7" width="52.0"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
+    <col min="1" max="1" customWidth="1" width="16"/>
+    <col min="2" max="2" customWidth="1" width="28"/>
+    <col min="3" max="3" customWidth="1" width="32"/>
+    <col min="4" max="4" customWidth="1" width="40"/>
+    <col min="5" max="5" customWidth="1" width="60"/>
+    <col min="6" max="6" customWidth="1" width="9"/>
+    <col min="7" max="7" customWidth="1" width="52"/>
+    <col min="8" max="8" customWidth="1" width="8.71"/>
+    <col min="9" max="9" customWidth="1" width="8.71"/>
+    <col min="10" max="10" customWidth="1" width="8.71"/>
+    <col min="11" max="11" customWidth="1" width="8.71"/>
+    <col min="12" max="12" customWidth="1" width="8.71"/>
+    <col min="13" max="13" customWidth="1" width="8.71"/>
+    <col min="14" max="14" customWidth="1" width="8.71"/>
+    <col min="15" max="15" customWidth="1" width="8.71"/>
+    <col min="16" max="16" customWidth="1" width="8.71"/>
+    <col min="17" max="17" customWidth="1" width="8.71"/>
+    <col min="18" max="18" customWidth="1" width="8.71"/>
+    <col min="19" max="19" customWidth="1" width="8.71"/>
+    <col min="20" max="20" customWidth="1" width="8.71"/>
+    <col min="21" max="21" customWidth="1" width="8.71"/>
+    <col min="22" max="22" customWidth="1" width="8.71"/>
+    <col min="23" max="23" customWidth="1" width="8.71"/>
+    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col min="25" max="25" customWidth="1" width="8.71"/>
+    <col min="26" max="26" customWidth="1" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>91</v>
+      <c r="A1" t="str">
+        <v>Character</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Block ID</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Variation ID</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Variation Description</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Variation Text</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Priority</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Conditions</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>205</v>
+      <c r="A2" t="str">
+        <v>Marie</v>
+      </c>
+      <c r="B2" t="str">
+        <v>B_Marie_2_Historie_1</v>
+      </c>
+      <c r="C2" t="str">
+        <v>V_Marie_2_Historie_1_A</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Vystoupila veřejně</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Veřejně vystoupila proti režimu.</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>A_Marie_2_2_Ano</v>
       </c>
     </row>
     <row r="3">
-      <c r="C3" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F3" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>212</v>
+      <c r="C3" t="str">
+        <v>V_Marie_2_Historie_1_B</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Přispěla na fond</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Přispěla na stávkový fond a zbylo jí dost peněz.</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="F4" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>128</v>
+      <c r="C4" t="str">
+        <v>V_Marie_2_Historie_1_C</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Držela se v ústraní.</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>225</v>
+      <c r="A5" t="str">
+        <v>Antonin</v>
+      </c>
+      <c r="B5" t="str">
+        <v>B_Antonin_2_Auto_1</v>
+      </c>
+      <c r="C5" t="str">
+        <v>V_Antonin_2_Auto_1_A</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Auto dostal Mirek</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="str">
+        <v>A_Antonin_2_1_Mirek</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="F6" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>128</v>
+      <c r="C6" t="str">
+        <v>V_Antonin_2_Auto_1_B</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Auto si nechal.</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>236</v>
+      <c r="B7" t="str">
+        <v>B_Antonin_2_Auto_2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>V_Antonin_2_Auto_2_A</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Poslední projížďka</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Před předáním se s ním naposled projel.</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="str">
+        <v>A_Antonin_2_2_Ano</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>128</v>
+      <c r="C8" t="str">
+        <v>V_Antonin_2_Auto_2_B</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Fallback — nic se nestalo</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>245</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="F9" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>236</v>
+      <c r="B9" t="str">
+        <v>B_Antonin_2_Stavka_1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>V_Antonin_2_Stavka_1_A</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Podpořil stávku</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Stávku veřejně podpořil.</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v>A_Antonin_2_2_Ano</v>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>251</v>
+      <c r="C10" t="str">
+        <v>V_Antonin_2_Stavka_1_B</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Nepodpořil</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Ke stávce se nepřidal.</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="str">
+        <v>A_Antonin_2_2_Ne</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="F11" s="8">
-        <v>3.0</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>128</v>
+      <c r="C11" t="str">
+        <v>V_Antonin_2_Stavka_1_C</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Fallback — otázka se nekladla</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Stávka se ho netýkala.</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>173</v>
+      <c r="A12" t="str">
+        <v>Funkcionari</v>
+      </c>
+      <c r="B12" t="str">
+        <v>B_Funkcionari_2_Vedeni_1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>V_Funkcionari_2_Vedeni_1_A</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Aktivní vedení</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Vedení bylo aktivní.</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>S_Antonin_Activity &gt;= 5</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>128</v>
+      <c r="C13" t="str">
+        <v>V_Funkcionari_2_Vedeni_1_B</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Fallback</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Vedení bylo pasivní.</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="str">
+        <v>DEFAULT</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>265</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>266</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>267</v>
+      <c r="B14" t="str">
+        <v>B_Funkcionari_2_Zapis_1</v>
+      </c>
+      <c r="C14" t="str">
+        <v>V_Funkcionari_2_Zapis_1_A</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Jediná varianta = fallback</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Zápis ze schůze byl archivován.</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -12907,9 +12098,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1000"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/documents/fixture-platny.xlsx
+++ b/documents/fixture-platny.xlsx
@@ -9828,7 +9828,7 @@
         <v>Ano</v>
       </c>
       <c r="I16" t="str">
-        <v>HOUSEHOLD_DELETE(Marie, Mirek)</v>
+        <v>HOUSEHOLD_DISSOLVE(Marie, Mirek)</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/documents/fixture-platny.xlsx
+++ b/documents/fixture-platny.xlsx
@@ -1,61 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="NOTES" sheetId="1" r:id="rId1"/>
-    <sheet name="Characters" sheetId="2" r:id="rId2"/>
-    <sheet name="Groups" sheetId="3" r:id="rId3"/>
-    <sheet name="Scales" sheetId="4" r:id="rId4"/>
-    <sheet name="Resources" sheetId="5" r:id="rId5"/>
-    <sheet name="1_Questions" sheetId="6" r:id="rId6"/>
-    <sheet name="2_Content" sheetId="7" r:id="rId7"/>
-    <sheet name="2_Questions" sheetId="8" r:id="rId8"/>
-    <sheet name="3_Content" sheetId="9" r:id="rId9"/>
-    <sheet name="3_Questions" sheetId="10" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Characters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scales" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Content" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Questions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Content" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Questions" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -73,14 +54,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -279,50 +328,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="110"/>
-    <col min="2" max="2" customWidth="1" width="8.71"/>
-    <col min="3" max="3" customWidth="1" width="8.71"/>
-    <col min="4" max="4" customWidth="1" width="8.71"/>
-    <col min="5" max="5" customWidth="1" width="8.71"/>
-    <col min="6" max="6" customWidth="1" width="8.71"/>
-    <col min="7" max="7" customWidth="1" width="8.71"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="8.710000000000001" customWidth="1" min="2" max="2"/>
+    <col width="8.710000000000001" customWidth="1" min="3" max="3"/>
+    <col width="8.710000000000001" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="8.710000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.710000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Fixture — platný (testovací data, ne skutečná hra)</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fixture — platný (testovací data, ne skutečná hra)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Musí projít importem bez chyb. Očekávaná varování a přehled pokrytí: fixtures-ocekavane-vysledky.md</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>List NOTES není součástí konfigurace — importér ho ignoruje (stejně jako v ukázkové tabulce autora).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Sloupec Condition v N_Questions nese jen Variation ID z N_Content téže kapitoly (§4.5). Bloky …_Questions_… rozhodují jen o otázce, mají prázdný Variation Text a nemají značku v šabloně.</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -1307,135 +1374,191 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="44"/>
-    <col min="3" max="3" customWidth="1" width="18"/>
-    <col min="4" max="4" customWidth="1" width="13"/>
-    <col min="5" max="5" customWidth="1" width="60"/>
-    <col min="6" max="6" customWidth="1" width="36"/>
-    <col min="7" max="7" customWidth="1" width="28"/>
-    <col min="8" max="8" customWidth="1" width="52"/>
-    <col min="9" max="9" customWidth="1" width="18"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="C1" t="str">
-        <v>Questions</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Responses</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Scale and Resources Impact</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Effects</v>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Responses</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Scale and Resources Impact</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Effects</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Condition</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Type</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Text</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ID Answer</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Text response</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ID Answer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Text response</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="D3" t="str">
-        <v>bool</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Vstoupila jsi do nové strany?</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="H3" t="str">
-        <v>S_Marie_Regime-1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vstoupila jsi do nové strany?</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime-1</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="G4" t="str">
-        <v>Ne</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B5" t="str">
-        <v>S_Antonin_Activity &gt;= 5</v>
-      </c>
-      <c r="D5" t="str">
-        <v>single</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Vrátíš se do zaměstnání?</v>
-      </c>
-      <c r="F5" t="str">
-        <v>A_Antonin_3_1_Vratim</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Vrátím se</v>
-      </c>
-      <c r="H5" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Vrátíš se do zaměstnání?</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A_Antonin_3_1_Vratim</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Vrátím se</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="F6" t="str">
-        <v>A_Antonin_3_1_Zustanu</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Zůstanu v důchodu</v>
-      </c>
-      <c r="H6" t="str">
-        <v>S_Antonin_Activity-1</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A_Antonin_3_1_Zustanu</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Zůstanu v důchodu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity-1</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2424,102 +2547,136 @@
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="18"/>
-    <col min="3" max="3" customWidth="1" width="18"/>
-    <col min="4" max="4" customWidth="1" width="22.29"/>
-    <col min="5" max="5" customWidth="1" width="8.71"/>
-    <col min="6" max="6" customWidth="1" width="8.71"/>
-    <col min="7" max="7" customWidth="1" width="8.71"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22.29" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="8.710000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.710000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Characters</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Characters</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Surname</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Household</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Surname</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Household</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Balážová</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Balážová</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Antonín</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Hájek</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Antonín</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hájek</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="B5" t="str">
-        <v xml:space="preserve"> Mirek</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Pokorný</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mirek</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pokorný</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Organizatori</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Organizátoři</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Organizatori</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Organizátoři</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -3507,69 +3664,85 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="18"/>
-    <col min="3" max="3" customWidth="1" width="8.71"/>
-    <col min="4" max="4" customWidth="1" width="8.71"/>
-    <col min="5" max="5" customWidth="1" width="8.71"/>
-    <col min="6" max="6" customWidth="1" width="8.71"/>
-    <col min="7" max="7" customWidth="1" width="8.71"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="8.710000000000001" customWidth="1" min="3" max="3"/>
+    <col width="8.710000000000001" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="8.710000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.710000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Groups</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Groups</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Name</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Funkcionari</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Funkcionáři</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Funkcionari</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Funkcionáři</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>SrdceParty</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Srdce party</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SrdceParty</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Srdce party</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -4557,128 +4730,156 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="24"/>
-    <col min="3" max="3" customWidth="1" width="8"/>
-    <col min="4" max="4" customWidth="1" width="8"/>
-    <col min="5" max="5" customWidth="1" width="10"/>
-    <col min="6" max="6" customWidth="1" width="8.71"/>
-    <col min="7" max="7" customWidth="1" width="8.71"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8.710000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.710000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
-        <v>Scales</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Scales</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Min</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Max</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Default</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B3" t="str">
-        <v>S_Marie_Regime</v>
-      </c>
-      <c r="C3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="str">
-        <v xml:space="preserve">S_Marie_Control </v>
-      </c>
-      <c r="C4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S_Marie_Control </t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B5" t="str">
-        <v>S_Antonin_Activity</v>
-      </c>
-      <c r="C5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="B6" t="str">
-        <v>S_Mirek_Regime</v>
-      </c>
-      <c r="C6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S_Mirek_Regime</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>10</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5667,90 +5868,112 @@
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="24"/>
-    <col min="3" max="3" customWidth="1" width="10"/>
-    <col min="4" max="4" customWidth="1" width="8.71"/>
-    <col min="5" max="5" customWidth="1" width="8.71"/>
-    <col min="6" max="6" customWidth="1" width="8.71"/>
-    <col min="7" max="7" customWidth="1" width="8.71"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8.710000000000001" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="8.710000000000001" customWidth="1" min="6" max="6"/>
+    <col width="8.710000000000001" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
-        <v>Resources</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Resources</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Default</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B3" t="str">
-        <v>R_Marie_Wealth</v>
-      </c>
-      <c r="C3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B4" t="str">
-        <v>R_Antonin_Wealth</v>
-      </c>
-      <c r="C4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R_Antonin_Wealth</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>50</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="B5" t="str">
-        <v>R_Mirek_Wealth</v>
-      </c>
-      <c r="C5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R_Mirek_Wealth</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6739,362 +6962,546 @@
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="18"/>
-    <col min="3" max="3" customWidth="1" width="13"/>
-    <col min="4" max="4" customWidth="1" width="60"/>
-    <col min="5" max="5" customWidth="1" width="36"/>
-    <col min="6" max="6" customWidth="1" width="28"/>
-    <col min="7" max="7" customWidth="1" width="46"/>
-    <col min="8" max="8" customWidth="1" width="18"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="str">
-        <v>Questions</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Responses</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Scale and Resources Impact</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Effects</v>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Responses</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Scale and Resources Impact</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Effects</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Type</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Text</v>
-      </c>
-      <c r="E2" t="str">
-        <v>ID Answer</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Text response</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ID Answer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Text response</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Q_Marie_1_1</v>
-      </c>
-      <c r="C3" t="str">
-        <v>single</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Kdo by měl vést partu ochránců přírody?</v>
-      </c>
-      <c r="E3" t="str">
-        <v>A_Marie_1_1_Antonin</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Antonín</v>
-      </c>
-      <c r="G3" t="str">
-        <v>R_Marie_Wealth+3, S_Marie_Regime-2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Q_Marie_1_1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kdo by měl vést partu ochránců přírody?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A_Marie_1_1_Antonin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Antonín</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth+3, S_Marie_Regime-2</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="E4" t="str">
-        <v>A_Marie_1_1_Mirek</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="G4" t="str">
-        <v>R_Marie_Wealth+1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>A_Marie_1_1_Mirek</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth+1</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="str">
-        <v>multi</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</v>
-      </c>
-      <c r="E5" t="str">
-        <v xml:space="preserve">A_Marie_1_2_Nikdo </v>
-      </c>
-      <c r="F5" t="str">
-        <v>Nikdo</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Podaří se Marii sehnat podporu pro lokální verzi Ekofilmu? Kdo přislíbil pomoc s organizací?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A_Marie_1_2_Nikdo </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nikdo</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="E6" t="str">
-        <v>A_Marie_1_2_Antonin</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Antonín</v>
-      </c>
-      <c r="G6" t="str">
-        <v>S_Marie_Regime+1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A_Marie_1_2_Antonin</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Antonín</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime+1</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="E7" t="str">
-        <v>A_Marie_1_2_Mirek</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="G7" t="str">
-        <v>R_Marie_Wealth+5; S_Marie_Control+1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A_Marie_1_2_Mirek</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth+5; S_Marie_Control+1</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="E8" t="str">
-        <v>A_Marie_1_2_Other</v>
-      </c>
-      <c r="F8" t="str">
-        <v>_OTHER_</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A_Marie_1_2_Other</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>_OTHER_</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="str">
-        <v>bool</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Vybrali tě za novou členku skupiny Srdce party?</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="G9" t="str">
-        <v>S_Marie_Regime-2</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Vybrali tě za novou členku skupiny Srdce party?</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime-2</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Antonín</v>
-      </c>
-      <c r="C10" t="str">
-        <v>single</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</v>
-      </c>
-      <c r="E10" t="str">
-        <v>A_Antonin_1_1_Prace</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Práce</v>
-      </c>
-      <c r="G10" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Antonín</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Zůstaneš v práci (na méně zodpovědné pozici), nebo půjdeš do důchodu, aby ses mohl víc starat o Věru?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_1_Prace</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Práce</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="E11" t="str">
-        <v>A_Antonin_1_1_Duchod</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Důchod</v>
-      </c>
-      <c r="G11" t="str">
-        <v>S_Antonin_Activity-1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_1_Duchod</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Důchod</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity-1</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="str">
-        <v>single</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</v>
-      </c>
-      <c r="E12" t="str">
-        <v>A_Antonin_1_2_Deti</v>
-      </c>
-      <c r="F12" t="str">
-        <v>Děti</v>
-      </c>
-      <c r="G12" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Budeš se aktivně starat o malé děti v okolí, jako to dřív dělala Věra, nebo budeš mít radši svůj klid?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_2_Deti</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Děti</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="E13" t="str">
-        <v>A_Antonin_1_2_Klid</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Klid</v>
-      </c>
-      <c r="G13" t="str">
-        <v>S_Antonin_Activity-1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_2_Klid</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Klid</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity-1</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="C14" t="str">
-        <v>poll-answer</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Q_Group_Funkcionari_Nastupce</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>poll-answer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q_Group_Funkcionari_Nastupce</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="str">
-        <v>single</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Fotil jsi:</v>
-      </c>
-      <c r="E15" t="str">
-        <v>A_Antonin_1_4_Funkcionare</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Funkcionáře</v>
-      </c>
-      <c r="G15" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fotil jsi:</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_4_Funkcionare</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Funkcionáře</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="E16" t="str">
-        <v>A_Antonin_1_4_Milovniky</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Milovníky přírody</v>
-      </c>
-      <c r="G16" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_4_Milovniky</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Milovníky přírody</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="E17" t="str">
-        <v>A_Antonin_1_4_Nikoho</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Nikoho</v>
-      </c>
-      <c r="G17" t="str">
-        <v>S_Antonin_Activity-1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_4_Nikoho</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Nikoho</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity-1</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="C18" t="str">
-        <v>poll-answer</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Q_Group_Funkcionari_Nastupce</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>poll-answer</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q_Group_Funkcionari_Nastupce</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>Organizatori</v>
-      </c>
-      <c r="C19" t="str">
-        <v>bool</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Došlo ke sňatku Marie a Mirka?</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="H19" t="str">
-        <v>HOUSEHOLD_CREATE(Marie, Mirek)</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Organizatori</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Došlo ke sňatku Marie a Mirka?</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD_CREATE(Marie, Mirek)</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="str">
-        <v>scale_direct</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Nastav Mirkovu hodnotu Regime po poradě orgů.</v>
-      </c>
-      <c r="E20" t="str">
-        <v>A_Organizatori_1_2_Nastaveni</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Nová hodnota</v>
-      </c>
-      <c r="G20" t="str">
-        <v>S_Mirek_Regime=VALUE</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>scale_direct</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nastav Mirkovu hodnotu Regime po poradě orgů.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>A_Organizatori_1_2_Nastaveni</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nová hodnota</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S_Mirek_Regime=VALUE</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="C21" t="str">
-        <v>resource_direct</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Nastav osobní účet Antonína po poradě orgů.</v>
-      </c>
-      <c r="E21" t="str">
-        <v>A_Organizatori_1_3_Nastaveni</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Nová hodnota</v>
-      </c>
-      <c r="G21" t="str">
-        <v>R_Antonin_Wealth_private=VALUE</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>resource_direct</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nastav osobní účet Antonína po poradě orgů.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A_Organizatori_1_3_Nastaveni</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nová hodnota</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>R_Antonin_Wealth_private=VALUE</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="B23" t="str">
-        <v>Q_Group_Funkcionari_Nastupce</v>
-      </c>
-      <c r="C23" t="str">
-        <v>poll</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Kdo by se podle tebe měl stát novým vedoucím směny?</v>
-      </c>
-      <c r="E23" t="str">
-        <v>A_Group_Funkcionari_Nastupce_Antonin</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Antonín Hájek</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Q_Group_Funkcionari_Nastupce</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>poll</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kdo by se podle tebe měl stát novým vedoucím směny?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>A_Group_Funkcionari_Nastupce_Antonin</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Antonín Hájek</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="E24" t="str">
-        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Mirek Pokorný</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>A_Group_Funkcionari_Nastupce_Mirek</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mirek Pokorný</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
@@ -8079,523 +8486,890 @@
     <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="28"/>
-    <col min="3" max="3" customWidth="1" width="32"/>
-    <col min="4" max="4" customWidth="1" width="40"/>
-    <col min="5" max="5" customWidth="1" width="60"/>
-    <col min="6" max="6" customWidth="1" width="9"/>
-    <col min="7" max="7" customWidth="1" width="52"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Block ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Variation ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Variation Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Variation Text</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Conditions</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Block ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variation ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variation Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variation Text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B2" t="str">
-        <v>B_Marie_1_Historie_1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>V_Marie_1_Historie_1_A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Antonín vede partu a Marie je radikální</v>
-      </c>
-      <c r="E2" t="str">
-        <v>V uplynulém roce podpořila vedení party a její postoj k režimu se zostřil.</v>
-      </c>
-      <c r="F2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B_Marie_1_Historie_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_1_A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Antonín vede partu a Marie je radikální</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>V uplynulém roce podpořila vedení party a její postoj k režimu se zostřil.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="str">
-        <v>A_Marie_1_1_Antonin AND S_Marie_Regime &gt;= 5</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A_Marie_1_1_Antonin AND S_Marie_Regime &gt;= 5</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="str">
-        <v>V_Marie_1_Historie_1_B</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Antonín vede partu, nikdo jí nepomáhá</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Vedení party přijala s rezervou a o pomoc s Ekofilmem nikoho nepožádala.</v>
-      </c>
-      <c r="F3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_1_B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Antonín vede partu, nikdo jí nepomáhá</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vedení party přijala s rezervou a o pomoc s Ekofilmem nikoho nepožádala.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="str">
-        <v>A_Marie_1_1_Antonin AND !(A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A_Marie_1_1_Antonin AND !(A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="str">
-        <v>V_Marie_1_Historie_1_C</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Náhoda 50 %</v>
-      </c>
-      <c r="E4" t="str">
-        <v>V uplynulém roce si pořídila kocoura.</v>
-      </c>
-      <c r="F4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_1_C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Náhoda 50 %</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>V uplynulém roce si pořídila kocoura.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="str">
-        <v>!A_Marie_1_1_Antonin AND RANDOM(50)</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>!A_Marie_1_1_Antonin AND RANDOM(50)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="C5" t="str">
-        <v>V_Marie_1_Historie_1_D</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Dobře se jí daří — text záměrně prázdný (nic se nestalo)</v>
-      </c>
-      <c r="F5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_1_D</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Dobře se jí daří — text záměrně prázdný (nic se nestalo)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="str">
-        <v>R_Marie_Wealth &gt;= 7</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth &gt;= 7</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="str">
-        <v>V_Marie_1_Historie_1_E</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Fallback + zanořený blok</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Rok proběhl bez zásadních změn. {BLOK B_Marie_1_Historie_2}</v>
-      </c>
-      <c r="F6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_1_E</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fallback + zanořený blok</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rok proběhl bez zásadních změn. {BLOK B_Marie_1_Historie_2}</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="G6" t="str">
-        <v>DEFAULT</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
-        <v>B_Marie_1_Historie_2</v>
-      </c>
-      <c r="C7" t="str">
-        <v>V_Marie_1_Historie_2_A</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Přijata do Srdce party</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Byla přijata do Srdce party.</v>
-      </c>
-      <c r="F7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B_Marie_1_Historie_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_2_A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Přijata do Srdce party</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Byla přijata do Srdce party.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="str">
-        <v>A_Marie_1_3_Ano</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A_Marie_1_3_Ano</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="str">
-        <v>V_Marie_1_Historie_2_B</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Nepřijata (odpověď Ne bez řádku v listu)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Do Srdce party přijata nebyla.</v>
-      </c>
-      <c r="F8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_2_B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Nepřijata (odpověď Ne bez řádku v listu)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Do Srdce party přijata nebyla.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="str">
-        <v>A_Marie_1_3_Ne</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A_Marie_1_3_Ne</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="str">
-        <v>V_Marie_1_Historie_2_C</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Fallback s prázdnou podmínkou i textem</v>
-      </c>
-      <c r="F9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Historie_2_C</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Fallback s prázdnou podmínkou i textem</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="str">
-        <v>B_Marie_1_Questions_1</v>
-      </c>
-      <c r="C10" t="str">
-        <v>V_Marie_1_Questions_1_A</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Bez priority — rozhoduje pořadí řádků</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Doplňující otázka A pro další kapitolu.</v>
-      </c>
-      <c r="G10" t="str">
-        <v>!A_Marie_1_1_Antonin</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>B_Marie_1_Questions_1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rozhoduje o otázce o Ekofilmu (bez priority — pořadí řádků)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>!A_Marie_1_1_Antonin</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="str">
-        <v>V_Marie_1_Questions_1_B</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Fallback (prázdná podmínka)</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Doplňující otázka B pro další kapitolu.</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_1_B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fallback (prázdná podmínka) — otázka se nepoloží</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B12" t="str">
-        <v>B_Antonin_1_Historie_1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>V_Antonin_1_Historie_1_A</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Je plně v důchodu</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Je plně v důchodu.</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="str">
-        <v>A_Antonin_1_1_Duchod</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B_Marie_1_Questions_2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_2_A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rozhoduje o otázce „Vystoupíš veřejně proti režimu?"</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime &gt;= 5 AND (A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="str">
-        <v>V_Antonin_1_Historie_1_B</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Pracuje jako vrátný</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Pracuje jako vrátný při důchodu.</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" t="str">
-        <v>DEFAULT</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_2_B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fallback — otázka se nepoloží</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="str">
-        <v>B_Antonin_1_Historie_2</v>
-      </c>
-      <c r="C14" t="str">
-        <v>V_Antonin_1_Historie_2_A</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Vedoucím směny se stal Mirek</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Vedoucím směny se stal mladší kolega.</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="str">
-        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B_Marie_1_Questions_3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_3_A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Rozhoduje o otázce „Přispěješ na stávkový fond?"</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth &gt;= 7</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" t="str">
-        <v>V_Antonin_1_Historie_2_B</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Zůstává on</v>
-      </c>
-      <c r="E15" t="str">
-        <v>Vedoucím směny zůstal on sám.</v>
-      </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
-      <c r="G15" t="str">
-        <v>DEFAULT</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_3_B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fallback — otázka se nepoloží</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="str">
-        <v>B_Antonin_1_Historie_3</v>
-      </c>
-      <c r="C16" t="str">
-        <v>V_Antonin_1_Historie_3_C</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Fallback stojí na řádku první, ale má nejvyšší číslo</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Rok byl klidný.</v>
-      </c>
-      <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16" t="str">
-        <v>DEFAULT</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B_Antonin_1_Historie_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_1_A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Je plně v důchodu</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Je plně v důchodu.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_1_Duchod</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="C17" t="str">
-        <v>V_Antonin_1_Historie_3_A</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Aktivní + hlídá děti</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Rok byl plný práce a hlídání dětí v okolí.</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="str">
-        <v>A_Antonin_1_2_Deti AND S_Antonin_Activity &gt;= 5</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_1_B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pracuje jako vrátný</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pracuje jako vrátný při důchodu.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="C18" t="str">
-        <v>V_Antonin_1_Historie_3_B</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Aktivní</v>
-      </c>
-      <c r="E18" t="str">
-        <v>Rok byl plný práce.</v>
-      </c>
-      <c r="F18">
-        <v>2</v>
-      </c>
-      <c r="G18" t="str">
-        <v>S_Antonin_Activity &gt;= 5</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B_Antonin_1_Historie_2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_2_A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Vedoucím směny se stal Mirek</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vedoucím směny se stal mladší kolega.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A_Group_Funkcionari_Nastupce_Mirek</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="str">
-        <v>B_Antonin_1_Foto_1</v>
-      </c>
-      <c r="C19" t="str">
-        <v>V_Antonin_1_Foto_1_A</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Fotil funkcionáře</v>
-      </c>
-      <c r="E19" t="str">
-        <v>Fotil funkcionáře.</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="str">
-        <v>A_Antonin_1_4_Funkcionare</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_2_B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Zůstává on</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vedoucím směny zůstal on sám.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="C20" t="str">
-        <v>V_Antonin_1_Foto_1_B</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Fallback (prázdná podmínka)</v>
-      </c>
-      <c r="E20" t="str">
-        <v>Fotil něco jiného.</v>
-      </c>
-      <c r="F20">
-        <v>2</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B_Antonin_1_Historie_3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_3_C</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Fallback stojí na řádku první, ale má nejvyšší číslo</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rok byl klidný.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" xml:space="preserve">
-      <c r="A21" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="B21" t="str">
-        <v>B_Mirek_1_Historie_1</v>
-      </c>
-      <c r="C21" t="str">
-        <v>V_Mirek_1_Historie_1_A</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Vyhrál anketu</v>
-      </c>
-      <c r="E21" t="str">
-        <v>Stal se vedoucím směny.</v>
-      </c>
-      <c r="F21">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_3_A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Aktivní + hlídá děti</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rok byl plný práce a hlídání dětí v okolí.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>1</v>
       </c>
-      <c r="G21" t="str" xml:space="preserve">
-        <v xml:space="preserve">A_Group_Funkcionari_Nastupce_Mirek
-</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_2_Deti AND S_Antonin_Activity &gt;= 5</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="C22" t="str">
-        <v>V_Mirek_1_Historie_1_B</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E22" t="str">
-        <v>Vedoucím směny se nestal.</v>
-      </c>
-      <c r="F22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Historie_3_B</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Aktivní</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rok byl plný práce.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="str">
-        <v>DEFAULT</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity &gt;= 5</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" t="str">
-        <v>Funkcionari</v>
-      </c>
-      <c r="B23" t="str">
-        <v>B_Funkcionari_1_Vedeni_1</v>
-      </c>
-      <c r="C23" t="str">
-        <v>V_Funkcionari_1_Vedeni_1_A</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Nový vedoucí Mirek</v>
-      </c>
-      <c r="E23" t="str">
-        <v>Vedení převzal mladší člen.</v>
-      </c>
-      <c r="F23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B_Antonin_1_Foto_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Foto_1_A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fotil funkcionáře</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Fotil funkcionáře.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" t="str">
-        <v>A_Group_Funkcionari_Nastupce_Mirek</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_4_Funkcionare</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" t="str">
-        <v>V_Funkcionari_1_Vedeni_1_B</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E24" t="str">
-        <v>Vedení zůstalo beze změny.</v>
-      </c>
-      <c r="F24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Foto_1_B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Fallback (prázdná podmínka)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Fotil něco jiného.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>2</v>
-      </c>
-      <c r="G24" t="str">
-        <v>DEFAULT</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" t="str">
-        <v>SrdceParty</v>
-      </c>
-      <c r="B25" t="str">
-        <v>B_SrdceParty_1_Clenove_1</v>
-      </c>
-      <c r="C25" t="str">
-        <v>V_SrdceParty_1_Clenove_1_A</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Marie přijata</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Skupina přijala nového člena.</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="str">
-        <v>A_Marie_1_3_Ano</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B_Antonin_1_Questions_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rozhoduje o otázce o ekologické stávce</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A_Antonin_1_1_Prace</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" t="str">
-        <v>V_SrdceParty_1_Clenove_1_B</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Složení skupiny se nezměnilo.</v>
-      </c>
-      <c r="F26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Questions_1_B</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fallback — otázka se nepoloží</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>B_Mirek_1_Historie_1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>V_Mirek_1_Historie_1_A</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Vyhrál anketu</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Stal se vedoucím směny.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A_Group_Funkcionari_Nastupce_Mirek
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>V_Mirek_1_Historie_1_B</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Vedoucím směny se nestal.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="G26" t="str">
-        <v>DEFAULT</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Funkcionari</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B_Funkcionari_1_Vedeni_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>V_Funkcionari_1_Vedeni_1_A</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Nový vedoucí Mirek</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Vedení převzal mladší člen.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>A_Group_Funkcionari_Nastupce_Mirek</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>V_Funkcionari_1_Vedeni_1_B</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Vedení zůstalo beze změny.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SrdceParty</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>B_SrdceParty_1_Clenove_1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>V_SrdceParty_1_Clenove_1_A</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Marie přijata</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Skupina přijala nového člena.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>A_Marie_1_3_Ano</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>V_SrdceParty_1_Clenove_1_B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Složení skupiny se nezměnilo.</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+    </row>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -9566,269 +10340,396 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="44"/>
-    <col min="3" max="3" customWidth="1" width="18"/>
-    <col min="4" max="4" customWidth="1" width="13"/>
-    <col min="5" max="5" customWidth="1" width="60"/>
-    <col min="6" max="6" customWidth="1" width="36"/>
-    <col min="7" max="7" customWidth="1" width="28"/>
-    <col min="8" max="8" customWidth="1" width="52"/>
-    <col min="9" max="9" customWidth="1" width="18"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="C1" t="str">
-        <v>Questions</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Responses</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Scale and Resources Impact</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Effects</v>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Questions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Responses</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Scale and Resources Impact</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Effects</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Condition</v>
-      </c>
-      <c r="C2" t="str">
-        <v>ID</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Type</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Text</v>
-      </c>
-      <c r="F2" t="str">
-        <v>ID Answer</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Text response</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ID Answer</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Text response</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B3" t="str">
-        <v>!A_Marie_1_1_Antonin</v>
-      </c>
-      <c r="D3" t="str">
-        <v>multi</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Podaří se Marii zorganizovat lokální verzi Ekofilmu? Kdo přislíbil pomoc?</v>
-      </c>
-      <c r="F3" t="str">
-        <v>A_Marie_2_1_Nikdo</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Nikdo</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Podaří se Marii zorganizovat lokální verzi Ekofilmu? Kdo přislíbil pomoc?</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A_Marie_2_1_Nikdo</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Nikdo</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="F4" t="str">
-        <v>A_Marie_2_1_Antonin</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Antonín</v>
-      </c>
-      <c r="H4" t="str">
-        <v>S_Marie_Control+1</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>A_Marie_2_1_Antonin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Antonín</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>S_Marie_Control+1</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="F5" t="str">
-        <v>A_Marie_2_1_Mirek</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="H5" t="str">
-        <v>R_Marie_Wealth+2</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>A_Marie_2_1_Mirek</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth+2</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="F6" t="str">
-        <v>A_Marie_2_1_Other</v>
-      </c>
-      <c r="G6" t="str">
-        <v>_OTHER_</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>A_Marie_2_1_Other</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>_OTHER_</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
-        <v>S_Marie_Regime &gt;= 5 AND (A_Marie_1_2_Antonin OR A_Marie_1_2_Mirek)</v>
-      </c>
-      <c r="D7" t="str">
-        <v>bool</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Vystoupíš veřejně proti režimu?</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="H7" t="str">
-        <v>S_Marie_Regime+2, S_Marie_Control-1</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_2_A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Vystoupíš veřejně proti režimu?</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>S_Marie_Regime+2, S_Marie_Control-1</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="G8" t="str">
-        <v>Ne</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="str">
-        <v>R_Marie_Wealth &gt;= 7</v>
-      </c>
-      <c r="D9" t="str">
-        <v>bool</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Přispěješ na stávkový fond?</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="H9" t="str">
-        <v>R_Marie_Wealth_private-3</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V_Marie_1_Questions_3_A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Přispěješ na stávkový fond?</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>R_Marie_Wealth_private-3</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="D10" t="str">
-        <v>single</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Komu daruješ automobil s garáží?</v>
-      </c>
-      <c r="F10" t="str">
-        <v>A_Antonin_2_1_Mirek</v>
-      </c>
-      <c r="G10" t="str">
-        <v>Mirek</v>
-      </c>
-      <c r="H10" t="str">
-        <v>R_Antonin_Wealth-10, R_Mirek_Wealth+10</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Komu daruješ automobil s garáží?</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_1_Mirek</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>R_Antonin_Wealth-10, R_Mirek_Wealth+10</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="F11" t="str">
-        <v>A_Antonin_2_1_Nikdo</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Nikomu</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_1_Nikdo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nikomu</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="str">
-        <v>A_Antonin_1_1_Prace</v>
-      </c>
-      <c r="D12" t="str">
-        <v>bool</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Podpoříš veřejně ekologickou stávku v podniku?</v>
-      </c>
-      <c r="F12" t="str">
-        <v>A_Antonin_2_2_Ano</v>
-      </c>
-      <c r="G12" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="H12" t="str">
-        <v>S_Antonin_Activity+1</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V_Antonin_1_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Podpoříš veřejně ekologickou stávku v podniku?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_2_Ano</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity+1</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="F13" t="str">
-        <v>A_Antonin_2_2_Ne</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Ne</v>
-      </c>
-      <c r="H13" t="str">
-        <v>S_Antonin_Activity-1</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_2_Ne</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ne</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity-1</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="str">
-        <v>DEFAULT</v>
-      </c>
-      <c r="D14" t="str">
-        <v>single</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Kdo má nést odpovědnost za nesrovnalosti ve skladu materiálu?</v>
-      </c>
-      <c r="F14" t="str">
-        <v>A_Antonin_2_3_Mirek</v>
-      </c>
-      <c r="G14" t="str">
-        <v>Mirek</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kdo má nést odpovědnost za nesrovnalosti ve skladu materiálu?</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_3_Mirek</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Mirek</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="F15" t="str">
-        <v>A_Antonin_2_3_Nikdo</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Nikdo</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_3_Nikdo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nikdo</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>Organizatori</v>
-      </c>
-      <c r="D16" t="str">
-        <v>bool</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Došlo k rozvodu Marie a Mirka?</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Ano</v>
-      </c>
-      <c r="I16" t="str">
-        <v>HOUSEHOLD_DISSOLVE(Marie, Mirek)</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Organizatori</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Došlo k rozvodu Marie a Mirka?</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>HOUSEHOLD_DELETE(Marie, Mirek)</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -10817,304 +11718,487 @@
     <mergeCell ref="F1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1000"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="16"/>
-    <col min="2" max="2" customWidth="1" width="28"/>
-    <col min="3" max="3" customWidth="1" width="32"/>
-    <col min="4" max="4" customWidth="1" width="40"/>
-    <col min="5" max="5" customWidth="1" width="60"/>
-    <col min="6" max="6" customWidth="1" width="9"/>
-    <col min="7" max="7" customWidth="1" width="52"/>
-    <col min="8" max="8" customWidth="1" width="8.71"/>
-    <col min="9" max="9" customWidth="1" width="8.71"/>
-    <col min="10" max="10" customWidth="1" width="8.71"/>
-    <col min="11" max="11" customWidth="1" width="8.71"/>
-    <col min="12" max="12" customWidth="1" width="8.71"/>
-    <col min="13" max="13" customWidth="1" width="8.71"/>
-    <col min="14" max="14" customWidth="1" width="8.71"/>
-    <col min="15" max="15" customWidth="1" width="8.71"/>
-    <col min="16" max="16" customWidth="1" width="8.71"/>
-    <col min="17" max="17" customWidth="1" width="8.71"/>
-    <col min="18" max="18" customWidth="1" width="8.71"/>
-    <col min="19" max="19" customWidth="1" width="8.71"/>
-    <col min="20" max="20" customWidth="1" width="8.71"/>
-    <col min="21" max="21" customWidth="1" width="8.71"/>
-    <col min="22" max="22" customWidth="1" width="8.71"/>
-    <col min="23" max="23" customWidth="1" width="8.71"/>
-    <col min="24" max="24" customWidth="1" width="8.71"/>
-    <col min="25" max="25" customWidth="1" width="8.71"/>
-    <col min="26" max="26" customWidth="1" width="8.71"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="8.710000000000001" customWidth="1" min="8" max="8"/>
+    <col width="8.710000000000001" customWidth="1" min="9" max="9"/>
+    <col width="8.710000000000001" customWidth="1" min="10" max="10"/>
+    <col width="8.710000000000001" customWidth="1" min="11" max="11"/>
+    <col width="8.710000000000001" customWidth="1" min="12" max="12"/>
+    <col width="8.710000000000001" customWidth="1" min="13" max="13"/>
+    <col width="8.710000000000001" customWidth="1" min="14" max="14"/>
+    <col width="8.710000000000001" customWidth="1" min="15" max="15"/>
+    <col width="8.710000000000001" customWidth="1" min="16" max="16"/>
+    <col width="8.710000000000001" customWidth="1" min="17" max="17"/>
+    <col width="8.710000000000001" customWidth="1" min="18" max="18"/>
+    <col width="8.710000000000001" customWidth="1" min="19" max="19"/>
+    <col width="8.710000000000001" customWidth="1" min="20" max="20"/>
+    <col width="8.710000000000001" customWidth="1" min="21" max="21"/>
+    <col width="8.710000000000001" customWidth="1" min="22" max="22"/>
+    <col width="8.710000000000001" customWidth="1" min="23" max="23"/>
+    <col width="8.710000000000001" customWidth="1" min="24" max="24"/>
+    <col width="8.710000000000001" customWidth="1" min="25" max="25"/>
+    <col width="8.710000000000001" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Character</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Block ID</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Variation ID</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Variation Description</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Variation Text</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Priority</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Conditions</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Block ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Variation ID</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Variation Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Variation Text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Conditions</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Marie</v>
-      </c>
-      <c r="B2" t="str">
-        <v>B_Marie_2_Historie_1</v>
-      </c>
-      <c r="C2" t="str">
-        <v>V_Marie_2_Historie_1_A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Vystoupila veřejně</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Veřejně vystoupila proti režimu.</v>
-      </c>
-      <c r="F2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Marie</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>B_Marie_2_Historie_1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>V_Marie_2_Historie_1_A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Vystoupila veřejně</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Veřejně vystoupila proti režimu.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="str">
-        <v>A_Marie_2_2_Ano</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>A_Marie_2_2_Ano</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="C3" t="str">
-        <v>V_Marie_2_Historie_1_B</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Přispěla na fond</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Přispěla na stávkový fond a zbylo jí dost peněz.</v>
-      </c>
-      <c r="F3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>V_Marie_2_Historie_1_B</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Přispěla na fond</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Přispěla na stávkový fond a zbylo jí dost peněz.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="str">
-        <v>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A_Marie_2_3_Ano AND R_Marie_Wealth &gt;= 7</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="str">
-        <v>V_Marie_2_Historie_1_C</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Držela se v ústraní.</v>
-      </c>
-      <c r="F4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>V_Marie_2_Historie_1_C</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Držela se v ústraní.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="str">
-        <v>DEFAULT</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Antonin</v>
-      </c>
-      <c r="B5" t="str">
-        <v>B_Antonin_2_Auto_1</v>
-      </c>
-      <c r="C5" t="str">
-        <v>V_Antonin_2_Auto_1_A</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Auto dostal Mirek</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</v>
-      </c>
-      <c r="F5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Antonin</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B_Antonin_2_Auto_1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Auto_1_A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Auto dostal Mirek</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Auto přepsal i s garáží na kamaráda. {BLOK B_Antonin_2_Auto_2}</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="str">
-        <v>A_Antonin_2_1_Mirek</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_1_Mirek</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="C6" t="str">
-        <v>V_Antonin_2_Auto_1_B</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Auto si nechal.</v>
-      </c>
-      <c r="F6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Auto_1_B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Auto si nechal.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="str">
-        <v>DEFAULT</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
-        <v>B_Antonin_2_Auto_2</v>
-      </c>
-      <c r="C7" t="str">
-        <v>V_Antonin_2_Auto_2_A</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Poslední projížďka</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Před předáním se s ním naposled projel.</v>
-      </c>
-      <c r="F7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>B_Antonin_2_Auto_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Auto_2_A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Poslední projížďka</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Před předáním se s ním naposled projel.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="str">
-        <v>A_Antonin_2_2_Ano</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_2_Ano</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="str">
-        <v>V_Antonin_2_Auto_2_B</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Fallback — nic se nestalo</v>
-      </c>
-      <c r="F8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Auto_2_B</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Fallback — nic se nestalo</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="str">
-        <v>DEFAULT</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="str">
-        <v>B_Antonin_2_Stavka_1</v>
-      </c>
-      <c r="C9" t="str">
-        <v>V_Antonin_2_Stavka_1_A</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Podpořil stávku</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Stávku veřejně podpořil.</v>
-      </c>
-      <c r="F9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>B_Antonin_2_Stavka_1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Stavka_1_A</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Podpořil stávku</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Stávku veřejně podpořil.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="str">
-        <v>A_Antonin_2_2_Ano</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_2_Ano</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="str">
-        <v>V_Antonin_2_Stavka_1_B</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Nepodpořil</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Ke stávce se nepřidal.</v>
-      </c>
-      <c r="F10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Stavka_1_B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nepodpořil</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ke stávce se nepřidal.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="str">
-        <v>A_Antonin_2_2_Ne</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A_Antonin_2_2_Ne</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="str">
-        <v>V_Antonin_2_Stavka_1_C</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Fallback — otázka se nekladla</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Stávka se ho netýkala.</v>
-      </c>
-      <c r="F11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Stavka_1_C</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Fallback — otázka se nekladla</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Stávka se ho netýkala.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="str">
-        <v>DEFAULT</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Funkcionari</v>
-      </c>
-      <c r="B12" t="str">
-        <v>B_Funkcionari_2_Vedeni_1</v>
-      </c>
-      <c r="C12" t="str">
-        <v>V_Funkcionari_2_Vedeni_1_A</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Aktivní vedení</v>
-      </c>
-      <c r="E12" t="str">
-        <v>Vedení bylo aktivní.</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="str">
-        <v>S_Antonin_Activity &gt;= 5</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B_Antonin_2_Questions_1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Questions_1_A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Rozhoduje o otázce „Vrátíš se do zaměstnání?"</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity &gt;= 5</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" t="str">
-        <v>V_Funkcionari_2_Vedeni_1_B</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Fallback</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Vedení bylo pasivní.</v>
-      </c>
-      <c r="F13">
-        <v>2</v>
-      </c>
-      <c r="G13" t="str">
-        <v>DEFAULT</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>V_Antonin_2_Questions_1_B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fallback — otázka se nepoloží</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="str">
-        <v>B_Funkcionari_2_Zapis_1</v>
-      </c>
-      <c r="C14" t="str">
-        <v>V_Funkcionari_2_Zapis_1_A</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Jediná varianta = fallback</v>
-      </c>
-      <c r="E14" t="str">
-        <v>Zápis ze schůze byl archivován.</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Funkcionari</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B_Funkcionari_2_Vedeni_1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>V_Funkcionari_2_Vedeni_1_A</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aktivní vedení</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Vedení bylo aktivní.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S_Antonin_Activity &gt;= 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>V_Funkcionari_2_Vedeni_1_B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Vedení bylo pasivní.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B_Funkcionari_2_Zapis_1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>V_Funkcionari_2_Zapis_1_A</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Jediná varianta = fallback</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Zápis ze schůze byl archivován.</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -12099,8 +13183,5 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1000"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/documents/fixture-platny.xlsx
+++ b/documents/fixture-platny.xlsx
@@ -10728,7 +10728,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>HOUSEHOLD_DELETE(Marie, Mirek)</t>
+          <t>HOUSEHOLD_DISSOLVE(Marie, Mirek)</t>
         </is>
       </c>
     </row>
